--- a/cfo-dashboard/downloads/cfo-dashboard.xlsx
+++ b/cfo-dashboard/downloads/cfo-dashboard.xlsx
@@ -13,8 +13,12 @@
     <sheet name="4. Deep Dive" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5. Forecast" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6. Trends" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7. Action Flags" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8. Raw snapshot.json" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="7. Segments" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8. Working Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9. Scenarios" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10. Industry Benchmark" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11. Action Flags" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12. Raw snapshot.json" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,9 +27,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]-&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -96,12 +101,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDF7E7"/>
+        <fgColor rgb="00FCE0E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE0E0"/>
+        <fgColor rgb="00DDF7E7"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -185,22 +190,28 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -840,6 +851,3462 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Industry Benchmark — Strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Commercial And Institutional Building Construction  ·  NAICS 236220  ·  IN  ·  Mar 2025 - Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Annualized profit (12-mo)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>3757685.49</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>IN regional average</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>101486.51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Above regional average by (live)</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <f>(B5-B6)/B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Multiple vs regional (live)</t>
+        </is>
+      </c>
+      <c r="B8" s="21">
+        <f>B5/B6</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Action Flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Computed live from current period vs prior + forecast. Severities: bad / warn / good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Triggered?</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Revenue trajectory above prior year</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>Run-rate $46,504,248 vs FY 2025 $40,491,815.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Gross margin compression vs prior year</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>BAD</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>GM% 27.19% vs prior 31.45% (-4.27pt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Negative net cash flow YTD</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>BAD</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>YTD net cash $-358,105 (Op $760,034 + Inv $212,852 + Fin $-1,330,992).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Negative cash position</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>BAD</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Cash at end of period $-602,043 (LoC drawn). Beginning $-243,938.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>A/R collection risk</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>Cash deteriorated by $-358,105 vs prior year-end.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H295"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Raw snapshot.json values</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source of truth for every other tab. Edit at your own risk — formulas elsewhere reference these.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>company.name</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Midwest Design Group LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>company.industry</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Commercial and Institutional Building Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>company.naics</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>company.state</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>asOf</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>generatedAt</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-07T04:02:32.164249+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>QuickBooks Online (live, via QuickBooks MCP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>personas[0].id</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>cfo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>personas[0].label</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>CFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>personas[0].kpis[0]</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>personas[0].kpis[1]</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>grossProfit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>personas[0].kpis[2]</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>netIncome</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>personas[0].kpis[3]</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>netMarginPct</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>personas[0].kpis[4]</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>cashEnding</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>personas[0].kpis[5]</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>yearEndForecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>personas[1].id</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>fpa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>personas[1].label</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>personas[1].kpis[0]</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>personas[1].kpis[1]</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>grossMarginPct</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>personas[1].kpis[2]</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>operatingExpenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>personas[1].kpis[3]</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>yearEndForecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>personas[1].kpis[4]</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>varianceVsForecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>personas[1].kpis[5]</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>monthlyTrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>personas[2].id</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>controller</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>personas[2].label</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>personas[2].kpis[0]</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>netIncome</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>personas[2].kpis[1]</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>operatingExpenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>personas[2].kpis[2]</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>personas[2].kpis[3]</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>ap</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>personas[2].kpis[4]</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>retainage</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>personas[2].kpis[5]</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>wipNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>personas[3].id</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>personas[3].label</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>personas[3].kpis[0]</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>personas[3].kpis[1]</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>yoyGrowth</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>personas[3].kpis[2]</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>twoYearCagr</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>personas[3].kpis[3]</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>vsRegional</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t>personas[3].kpis[4]</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>segmentMix</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>personas[3].kpis[5]</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>marginExpansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>personas[4].id</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>treasury</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>personas[4].label</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>Treasury</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>personas[4].kpis[0]</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>cashEnding</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>personas[4].kpis[1]</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>operatingCash</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>personas[4].kpis[2]</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>lineOfCreditDraw</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>personas[4].kpis[3]</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>yearEndCash</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>personas[4].kpis[4]</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>personas[4].kpis[5]</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>ap</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.periodStart</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.periodEnd</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.revenue</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>19376770.19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.cogs</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>14108989.66</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.grossProfit</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>5267780.53</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>3480138.73</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.netIncome</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1661587.75</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>0.2718606082616702</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.netMarginPct</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>0.08575153308354315</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[0].account</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Division Material Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[0].amount</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>20720.33</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[1].account</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Supply Arbor Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[1].amount</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>571765.41</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[2].account</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Supply Pulte Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[2].amount</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>16823.83</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[3].account</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>Engineering Project Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[3].amount</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>206725</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[4].account</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[4].amount</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>4820</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[5].account</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>Service/Fee Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[5].amount</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>15924134.62</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[6].account</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>WIP Adj - Net change</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.incomeAccounts[6].amount</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>2347599</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.cogsBuckets[0].bucket</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>Labor (contractors + direct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.cogsBuckets[0].amount</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>6261029.85</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.cogsBuckets[1].bucket</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>Materials &amp; supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.cogsBuckets[1].amount</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>2745051.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.cogsBuckets[2].bucket</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>Job site &amp; rental</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.cogsBuckets[2].amount</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>529849.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[0].bucket</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>Payroll &amp; benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[0].amount</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>1928101.09</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[1].bucket</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>Facilities (rent + utilities)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[1].amount</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>757455.8100000001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[2].bucket</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>Vehicle / fleet</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[2].amount</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>72850.52</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[3].bucket</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>Insurance &amp; professional</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[3].amount</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>191337.16</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[4].bucket</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>G&amp;A (office, IT, dues, travel, M&amp;E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[4].amount</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>64541.24</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[5].bucket</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>Other OpEx</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="29" t="inlineStr">
+        <is>
+          <t>periods.current.segments.opexBuckets[5].amount</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>221218.59</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.periodStart</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.periodEnd</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.revenue</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>40491815.42</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.cogs</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>27755136.44</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.grossProfit</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>12736678.98</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>9925912.359999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.netIncome</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>2810766.62</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="n">
+        <v>0.314549467537803</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.netMarginPct</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="n">
+        <v>0.06941567304022843</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[0].account</t>
+        </is>
+      </c>
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>Billable Expense Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[0].amount</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[1].account</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>Doors and Windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[1].amount</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>4594.5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[2].account</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Division Delivery Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[2].amount</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>201.04</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[3].account</t>
+        </is>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Division Material Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[3].amount</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>2824148.9</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[4].account</t>
+        </is>
+      </c>
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Supply Arbor Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[4].amount</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>959002.74</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[5].account</t>
+        </is>
+      </c>
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Supply Century Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[5].amount</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>105734.39</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[6].account</t>
+        </is>
+      </c>
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Supply HD Boom Scatter Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[6].amount</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>174372.44</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[7].account</t>
+        </is>
+      </c>
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Supply Pulte Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[7].amount</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>6230.22</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[8].account</t>
+        </is>
+      </c>
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[8].amount</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>67.77</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[9].account</t>
+        </is>
+      </c>
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>Engineering Project Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[9].amount</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>709295</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[10].account</t>
+        </is>
+      </c>
+      <c r="B122" s="13" t="inlineStr">
+        <is>
+          <t>Finishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[10].amount</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>76310.00999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[11].account</t>
+        </is>
+      </c>
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[11].amount</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>13469.39</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[12].account</t>
+        </is>
+      </c>
+      <c r="B126" s="13" t="inlineStr">
+        <is>
+          <t>Service/Fee Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[12].amount</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>33721642.66</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[13].account</t>
+        </is>
+      </c>
+      <c r="B128" s="13" t="inlineStr">
+        <is>
+          <t>Specialties</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[13].amount</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>2713.5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[14].account</t>
+        </is>
+      </c>
+      <c r="B130" s="13" t="inlineStr">
+        <is>
+          <t>WIP Adj - Net change</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.incomeAccounts[14].amount</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>-1464686.27</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.cogsBuckets[0].bucket</t>
+        </is>
+      </c>
+      <c r="B132" s="13" t="inlineStr">
+        <is>
+          <t>Labor (contractors + direct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.cogsBuckets[0].amount</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>213374.44</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.cogsBuckets[1].bucket</t>
+        </is>
+      </c>
+      <c r="B134" s="13" t="inlineStr">
+        <is>
+          <t>Materials &amp; supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.cogsBuckets[1].amount</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>9213980.66</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.cogsBuckets[2].bucket</t>
+        </is>
+      </c>
+      <c r="B136" s="13" t="inlineStr">
+        <is>
+          <t>Job site &amp; rental</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.cogsBuckets[2].amount</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>734785.45</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.cogsBuckets[3].bucket</t>
+        </is>
+      </c>
+      <c r="B138" s="13" t="inlineStr">
+        <is>
+          <t>Other COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.cogsBuckets[3].amount</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>-11150.24</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[0].bucket</t>
+        </is>
+      </c>
+      <c r="B140" s="13" t="inlineStr">
+        <is>
+          <t>Payroll &amp; benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[0].amount</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>5521265.96</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[1].bucket</t>
+        </is>
+      </c>
+      <c r="B142" s="13" t="inlineStr">
+        <is>
+          <t>Facilities (rent + utilities)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[1].amount</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>1286006.54</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[2].bucket</t>
+        </is>
+      </c>
+      <c r="B144" s="13" t="inlineStr">
+        <is>
+          <t>Vehicle / fleet</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[2].amount</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>267046.97</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[3].bucket</t>
+        </is>
+      </c>
+      <c r="B146" s="13" t="inlineStr">
+        <is>
+          <t>Insurance &amp; professional</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[3].amount</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>823266</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[4].bucket</t>
+        </is>
+      </c>
+      <c r="B148" s="13" t="inlineStr">
+        <is>
+          <t>G&amp;A (office, IT, dues, travel, M&amp;E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[4].amount</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>157841.59</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[5].bucket</t>
+        </is>
+      </c>
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>Other OpEx</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior.segments.opexBuckets[5].amount</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="n">
+        <v>981759.21</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior2.periodStart</t>
+        </is>
+      </c>
+      <c r="B152" s="13" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior2.periodEnd</t>
+        </is>
+      </c>
+      <c r="B153" s="13" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior2.revenue</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="n">
+        <v>39537774.9</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior2.cogs</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>28435216.93</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior2.grossProfit</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="n">
+        <v>11102557.97</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior2.operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="n">
+        <v>8249044.14</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior2.netIncome</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="n">
+        <v>2899162.56</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior2.grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="n">
+        <v>0.2808088719732179</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="29" t="inlineStr">
+        <is>
+          <t>periods.prior2.netMarginPct</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="n">
+        <v>0.07332639652415061</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.periodStart</t>
+        </is>
+      </c>
+      <c r="B161" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.periodEnd</t>
+        </is>
+      </c>
+      <c r="B162" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.operating</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="n">
+        <v>760034.3</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.investing</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="n">
+        <v>212852.1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.financing</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="n">
+        <v>-1330991.51</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.netCashChange</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="n">
+        <v>-358105.11</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.cashBeginning</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="n">
+        <v>-243937.55</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.cashEnding</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="n">
+        <v>-602042.66</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.netIncome</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="n">
+        <v>1661587.75</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.workingCapital.accountsPayableChange</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="n">
+        <v>286831.19</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.workingCapital.accountsReceivableChange</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="n">
+        <v>-649262.0699999999</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.workingCapital.retainageReceivableChange</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="n">
+        <v>-837450.48</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.workingCapital.inventoryDrywallChange</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="n">
+        <v>193111.88</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.workingCapital.wipOverbillingsChange</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>-1073267.83</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.workingCapital.wipUnderbillingsChange</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="n">
+        <v>-1274331.17</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.workingCapital.accruedBonusesChange</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="n">
+        <v>224000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.workingCapital.accruedPayrollChange</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="n">
+        <v>-149000</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.workingCapital.lineOfCreditDraw</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="n">
+        <v>2536373.04</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.current.workingCapital.lineOfCreditCapXChange</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="n">
+        <v>-27802.23</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.periodStart</t>
+        </is>
+      </c>
+      <c r="B180" s="13" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.periodEnd</t>
+        </is>
+      </c>
+      <c r="B181" s="13" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.operating</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="n">
+        <v>1607367.49</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.investing</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="n">
+        <v>179545.59</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.financing</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="n">
+        <v>-1432655.18</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.netCashChange</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="n">
+        <v>354257.9</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.cashBeginning</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>-598195.45</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.cashEnding</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>-243937.55</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.netIncome</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>2810766.62</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.accountsPayableChange</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>712464.46</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.accountsReceivableChange</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>-733947.11</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.retainageReceivableChange</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>-2438809.88</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.inventoryDrywallChange</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="n">
+        <v>362396.12</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.wipOverbillingsChange</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="n">
+        <v>1249606.34</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.wipUnderbillingsChange</t>
+        </is>
+      </c>
+      <c r="B194" s="5" t="n">
+        <v>215079.93</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.accruedBonusesChange</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="n">
+        <v>-9352.09</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.accruedPayrollChange</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.accruedCommissionsChange</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="n">
+        <v>-37000</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.lineOfCreditDraw</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="n">
+        <v>-460964.34</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.lineOfCreditCapXChange</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="n">
+        <v>-67265.75999999999</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.leaseLiabilityCurrentChange</t>
+        </is>
+      </c>
+      <c r="B200" s="5" t="n">
+        <v>-112868</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.leaseLiabilityNoncurrentChange</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="n">
+        <v>-959670</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="29" t="inlineStr">
+        <is>
+          <t>cashFlow.prior.workingCapital.rouAssetOperatingLeasesChange</t>
+        </is>
+      </c>
+      <c r="B202" s="5" t="n">
+        <v>967660</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.current.ar</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="n">
+        <v>-649262.0699999999</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.current.ap</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="n">
+        <v>286831.19</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.current.retainage</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="n">
+        <v>-837450.48</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.current.inventory</t>
+        </is>
+      </c>
+      <c r="B206" s="5" t="n">
+        <v>193111.88</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.current.wipOverbillings</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="n">
+        <v>-1073267.83</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.current.wipUnderbillings</t>
+        </is>
+      </c>
+      <c r="B208" s="5" t="n">
+        <v>-1274331.17</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.current.lineOfCreditDraw</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="n">
+        <v>2536373.04</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.current.totalWorkingCapitalChange</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="n">
+        <v>-3354368.48</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.prior.ar</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="n">
+        <v>-733947.11</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.prior.ap</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="n">
+        <v>712464.46</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.prior.retainage</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="n">
+        <v>-2438809.88</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.prior.inventory</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="n">
+        <v>362396.12</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.prior.wipOverbillings</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="n">
+        <v>1249606.34</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.prior.wipUnderbillings</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="n">
+        <v>215079.93</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.prior.lineOfCreditDraw</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="n">
+        <v>-460964.34</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="29" t="inlineStr">
+        <is>
+          <t>workingCapital.prior.totalWorkingCapitalChange</t>
+        </is>
+      </c>
+      <c r="B218" s="5" t="n">
+        <v>-633210.1399999997</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="29" t="inlineStr">
+        <is>
+          <t>forecast.completedMonths</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="29" t="inlineStr">
+        <is>
+          <t>forecast.remainingMonths</t>
+        </is>
+      </c>
+      <c r="B220" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="29" t="inlineStr">
+        <is>
+          <t>forecast.ytdRevenue</t>
+        </is>
+      </c>
+      <c r="B221" s="5" t="n">
+        <v>19376770.19</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="29" t="inlineStr">
+        <is>
+          <t>forecast.ytdGrossProfit</t>
+        </is>
+      </c>
+      <c r="B222" s="5" t="n">
+        <v>5267780.53</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="29" t="inlineStr">
+        <is>
+          <t>forecast.ytdOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="n">
+        <v>3480138.73</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="29" t="inlineStr">
+        <is>
+          <t>forecast.ytdNetIncome</t>
+        </is>
+      </c>
+      <c r="B224" s="5" t="n">
+        <v>1661587.75</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="29" t="inlineStr">
+        <is>
+          <t>forecast.avgMonthlyRevenue</t>
+        </is>
+      </c>
+      <c r="B225" s="5" t="n">
+        <v>3875354.04</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="29" t="inlineStr">
+        <is>
+          <t>forecast.avgMonthlyGrossProfit</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="n">
+        <v>1053556.11</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="29" t="inlineStr">
+        <is>
+          <t>forecast.avgMonthlyOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="B227" s="5" t="n">
+        <v>696027.75</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="29" t="inlineStr">
+        <is>
+          <t>forecast.avgMonthlyNetIncome</t>
+        </is>
+      </c>
+      <c r="B228" s="5" t="n">
+        <v>332317.55</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="29" t="inlineStr">
+        <is>
+          <t>forecast.yearEndRevenue</t>
+        </is>
+      </c>
+      <c r="B229" s="5" t="n">
+        <v>46504248.46</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="29" t="inlineStr">
+        <is>
+          <t>forecast.yearEndGrossProfit</t>
+        </is>
+      </c>
+      <c r="B230" s="5" t="n">
+        <v>12642673.27</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="29" t="inlineStr">
+        <is>
+          <t>forecast.yearEndOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="B231" s="5" t="n">
+        <v>8352332.95</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="29" t="inlineStr">
+        <is>
+          <t>forecast.yearEndNetIncome</t>
+        </is>
+      </c>
+      <c r="B232" s="5" t="n">
+        <v>3987810.6</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="29" t="inlineStr">
+        <is>
+          <t>forecast.runRateRevenue</t>
+        </is>
+      </c>
+      <c r="B233" s="5" t="n">
+        <v>46504248.46</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="29" t="inlineStr">
+        <is>
+          <t>forecast.runRateGrossProfit</t>
+        </is>
+      </c>
+      <c r="B234" s="5" t="n">
+        <v>12642673.27</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="29" t="inlineStr">
+        <is>
+          <t>forecast.runRateOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="B235" s="5" t="n">
+        <v>8352332.95</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="29" t="inlineStr">
+        <is>
+          <t>forecast.runRateNetIncome</t>
+        </is>
+      </c>
+      <c r="B236" s="5" t="n">
+        <v>3987810.6</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="29" t="inlineStr">
+        <is>
+          <t>forecast.yearEndGrossMarginPct</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="n">
+        <v>0.2718606081952797</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="29" t="inlineStr">
+        <is>
+          <t>forecast.yearEndNetMarginPct</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="n">
+        <v>0.08575153307616747</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="29" t="inlineStr">
+        <is>
+          <t>forecast.yearEndCash</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="n">
+        <v>-1103389.81</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="29" t="inlineStr">
+        <is>
+          <t>forecast.yearEndOperatingCash</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="n">
+        <v>1824082.32</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].periodStart</t>
+        </is>
+      </c>
+      <c r="B241" s="13" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].periodEnd</t>
+        </is>
+      </c>
+      <c r="B242" s="13" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].revenue</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="n">
+        <v>2041295.53</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].cogs</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="n">
+        <v>1705779.19</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].grossProfit</t>
+        </is>
+      </c>
+      <c r="B245" s="5" t="n">
+        <v>335516.34</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B246" s="5" t="n">
+        <v>917633.4300000001</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].netIncome</t>
+        </is>
+      </c>
+      <c r="B247" s="5" t="n">
+        <v>-582117</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B248" s="6" t="n">
+        <v>0.1643644122416709</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B249" s="6" t="n">
+        <v>-0.285170369231152</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].month</t>
+        </is>
+      </c>
+      <c r="B250" s="13" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].periodStart</t>
+        </is>
+      </c>
+      <c r="B251" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].periodEnd</t>
+        </is>
+      </c>
+      <c r="B252" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].revenue</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="n">
+        <v>2424157.48</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].cogs</t>
+        </is>
+      </c>
+      <c r="B254" s="5" t="n">
+        <v>1668995.34</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].grossProfit</t>
+        </is>
+      </c>
+      <c r="B255" s="5" t="n">
+        <v>755162.14</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B256" s="5" t="n">
+        <v>836162.72</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].netIncome</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="n">
+        <v>-69968.27</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B258" s="6" t="n">
+        <v>0.3115152980902874</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B259" s="6" t="n">
+        <v>-0.02886292271738056</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].month</t>
+        </is>
+      </c>
+      <c r="B260" s="13" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].periodStart</t>
+        </is>
+      </c>
+      <c r="B261" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].periodEnd</t>
+        </is>
+      </c>
+      <c r="B262" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].revenue</t>
+        </is>
+      </c>
+      <c r="B263" s="5" t="n">
+        <v>5290349.77</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].cogs</t>
+        </is>
+      </c>
+      <c r="B264" s="5" t="n">
+        <v>3616852.68</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].grossProfit</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="n">
+        <v>1673497.09</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="n">
+        <v>897079.72</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].netIncome</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="n">
+        <v>790908.5600000001</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="n">
+        <v>0.3163301412488649</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="n">
+        <v>0.1495002399434925</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].month</t>
+        </is>
+      </c>
+      <c r="B270" s="13" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].periodStart</t>
+        </is>
+      </c>
+      <c r="B271" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].periodEnd</t>
+        </is>
+      </c>
+      <c r="B272" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].revenue</t>
+        </is>
+      </c>
+      <c r="B273" s="5" t="n">
+        <v>4593904.49</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].cogs</t>
+        </is>
+      </c>
+      <c r="B274" s="5" t="n">
+        <v>3242912.67</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].grossProfit</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="n">
+        <v>1350991.82</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="n">
+        <v>713341.59</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].netIncome</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>677429.8100000001</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B278" s="6" t="n">
+        <v>0.2940835672445598</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B279" s="6" t="n">
+        <v>0.1474627544988424</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].month</t>
+        </is>
+      </c>
+      <c r="B280" s="13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.companyName</t>
+        </is>
+      </c>
+      <c r="B281" s="13" t="inlineStr">
+        <is>
+          <t>Midwest Design Group LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricType</t>
+        </is>
+      </c>
+      <c r="B282" s="13" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricLabel</t>
+        </is>
+      </c>
+      <c r="B283" s="13" t="inlineStr">
+        <is>
+          <t>Yearly Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricValue</t>
+        </is>
+      </c>
+      <c r="B284" s="5" t="n">
+        <v>3757685.49</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.regionalAverage</t>
+        </is>
+      </c>
+      <c r="B285" s="5" t="n">
+        <v>101486.51</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.nationalAverage</t>
+        </is>
+      </c>
+      <c r="B286" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.vsRegionalPercent</t>
+        </is>
+      </c>
+      <c r="B287" s="5" t="n">
+        <v>3602.65</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.vsNationalPercent</t>
+        </is>
+      </c>
+      <c r="B288" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.isAboveRegional</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.isAboveNational</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.location</t>
+        </is>
+      </c>
+      <c r="B291" s="13" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.naicsCode</t>
+        </is>
+      </c>
+      <c r="B292" s="13" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.industryType</t>
+        </is>
+      </c>
+      <c r="B293" s="13" t="inlineStr">
+        <is>
+          <t>Commercial And Institutional Building Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.benchmarkPeriodRange</t>
+        </is>
+      </c>
+      <c r="B294" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2025 - Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.reportDate</t>
+        </is>
+      </c>
+      <c r="B295" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2255,159 +5722,416 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Action Flags</t>
+          <t>Segments &amp; Cost Structure</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Computed live from current period vs prior + forecast. Severities: bad / warn / good.</t>
+          <t>Revenue mix, COGS structure, and OpEx structure for FP&amp;A and Strategy.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Flag</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Triggered?</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>Revenue trajectory above prior year</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>Run-rate $46,504,248 vs FY 2025 $40,491,815.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Gross margin compression vs prior year</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>BAD</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>GM% 27.19% vs prior 31.45% (-4.27pt).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Negative net cash flow YTD</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>BAD</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>YTD net cash $-358,105 (Op $760,034 + Inv $212,852 + Fin $-1,330,992).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Negative cash position</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>BAD</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>Cash at end of period $-602,043 (LoC drawn). Beginning $-243,938.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>A/R collection risk</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>Cash deteriorated by $-358,105 vs prior year-end.</t>
-        </is>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Revenue by income account</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>YTD 2026</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>% of revenue (live)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>FY 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Division Material Income</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>20720.33</v>
+      </c>
+      <c r="C6" s="6">
+        <f>B6/19376770.19</f>
+        <v/>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2824148.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Supply Arbor Income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>571765.41</v>
+      </c>
+      <c r="C7" s="6">
+        <f>B7/19376770.19</f>
+        <v/>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>959002.74</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Supply Pulte Income</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>16823.83</v>
+      </c>
+      <c r="C8" s="6">
+        <f>B8/19376770.19</f>
+        <v/>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>6230.22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Engineering Project Income</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>206725</v>
+      </c>
+      <c r="C9" s="6">
+        <f>B9/19376770.19</f>
+        <v/>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>709295</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>4820</v>
+      </c>
+      <c r="C10" s="6">
+        <f>B10/19376770.19</f>
+        <v/>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>13469.39</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Service/Fee Income</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>15924134.62</v>
+      </c>
+      <c r="C11" s="6">
+        <f>B11/19376770.19</f>
+        <v/>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>33721642.66</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>WIP Adj - Net change</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2347599</v>
+      </c>
+      <c r="C12" s="6">
+        <f>B12/19376770.19</f>
+        <v/>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-1464686.27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>COGS structure (3 buckets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>YTD 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>% of COGS (live)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>FY 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Labor (contractors + direct)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>6261029.85</v>
+      </c>
+      <c r="C17" s="6">
+        <f>B17/14108989.66</f>
+        <v/>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>213374.44</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Materials &amp; supply</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2745051.1</v>
+      </c>
+      <c r="C18" s="6">
+        <f>B18/14108989.66</f>
+        <v/>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>9213980.66</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Job site &amp; rental</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>529849.5</v>
+      </c>
+      <c r="C19" s="6">
+        <f>B19/14108989.66</f>
+        <v/>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>734785.45</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>OpEx structure (6 buckets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>YTD 2026</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>% of OpEx (live)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>FY 2025</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Δ %</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Payroll &amp; benefits</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1928101.09</v>
+      </c>
+      <c r="C24" s="6">
+        <f>B24/3480138.73</f>
+        <v/>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>5521265.96</v>
+      </c>
+      <c r="E24" s="6">
+        <f>IFERROR((B24-D24)/ABS(D24),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Facilities (rent + utilities)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>757455.8100000001</v>
+      </c>
+      <c r="C25" s="6">
+        <f>B25/3480138.73</f>
+        <v/>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1286006.54</v>
+      </c>
+      <c r="E25" s="6">
+        <f>IFERROR((B25-D25)/ABS(D25),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Vehicle / fleet</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>72850.52</v>
+      </c>
+      <c r="C26" s="6">
+        <f>B26/3480138.73</f>
+        <v/>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>267046.97</v>
+      </c>
+      <c r="E26" s="6">
+        <f>IFERROR((B26-D26)/ABS(D26),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Insurance &amp; professional</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>191337.16</v>
+      </c>
+      <c r="C27" s="6">
+        <f>B27/3480138.73</f>
+        <v/>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>823266</v>
+      </c>
+      <c r="E27" s="6">
+        <f>IFERROR((B27-D27)/ABS(D27),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>G&amp;A (office, IT, dues, travel, M&amp;E)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>64541.24</v>
+      </c>
+      <c r="C28" s="6">
+        <f>B28/3480138.73</f>
+        <v/>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>157841.59</v>
+      </c>
+      <c r="E28" s="6">
+        <f>IFERROR((B28-D28)/ABS(D28),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Other OpEx</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>221218.59</v>
+      </c>
+      <c r="C29" s="6">
+        <f>B29/3480138.73</f>
+        <v/>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>981759.21</v>
+      </c>
+      <c r="E29" s="6">
+        <f>IFERROR((B29-D29)/ABS(D29),"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2425,1203 +6149,446 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Raw snapshot.json values</t>
+          <t>Working Capital — Controller / Treasury view</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source of truth for every other tab. Edit at your own risk — formulas elsewhere reference these.</t>
+          <t>A/R, A/P, retainage, inventory, WIP. Drives free cash flow conversion.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Account</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>YTD 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>FY 2025</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Δ %</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Cash impact</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>company.name</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Midwest Design Group LLC</t>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>-649262.0699999999</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-733947.11</v>
+      </c>
+      <c r="D5" s="6">
+        <f>IFERROR((B5-C5)/ABS(C5),"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>Use of cash</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>company.industry</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Commercial and Institutional Building Construction</t>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>286831.19</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>712464.46</v>
+      </c>
+      <c r="D6" s="6">
+        <f>IFERROR((B6-C6)/ABS(C6),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>Source of cash</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>company.naics</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>236220</t>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Retainage Receivable</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>-837450.48</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>-2438809.88</v>
+      </c>
+      <c r="D7" s="6">
+        <f>IFERROR((B7-C7)/ABS(C7),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Use of cash</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>asOf</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Drywall Inventory</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>193111.88</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>362396.12</v>
+      </c>
+      <c r="D8" s="6">
+        <f>IFERROR((B8-C8)/ABS(C8),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Source of cash</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>generatedAt</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-07T03:26:00.310537+00:00</t>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>WIP Overbillings</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>-1073267.83</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1249606.34</v>
+      </c>
+      <c r="D9" s="6">
+        <f>IFERROR((B9-C9)/ABS(C9),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Use of cash</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>QuickBooks Online (live, via QuickBooks MCP)</t>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>WIP Underbillings</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>-1274331.17</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>215079.93</v>
+      </c>
+      <c r="D10" s="6">
+        <f>IFERROR((B10-C10)/ABS(C10),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Use of cash</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>periods.current.periodStart</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Line of Credit draw</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2536373.04</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-460964.34</v>
+      </c>
+      <c r="D11" s="6">
+        <f>IFERROR((B11-C11)/ABS(C11),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Source of cash</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>periods.current.periodEnd</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Total working-capital change (live sum)</t>
+        </is>
+      </c>
+      <c r="B12" s="17">
+        <f>SUM(B5:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="17">
+        <f>SUM(C5:C11)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario Modeling — FP&amp;A / Strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Inputs in B6:B8 are the only cells you edit. Year-end outcome below recomputes automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>YTD revenue (locked)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>19376770.19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2H revenue growth vs run-rate (e.g., 0.05 = +5%)</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Gross margin shift (pts; e.g., -0.01 = -1pt)</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>OpEx % vs run-rate (e.g., 0.10 = +10%)</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Year-end outcome (live)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Base forecast</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Δ vs base</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>46504248.46</v>
+      </c>
+      <c r="C12" s="5">
+        <f>B5+(3875354.04*7)*(1+$B$6)</f>
+        <v/>
+      </c>
+      <c r="D12" s="5">
+        <f>C12-B12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>periods.current.revenue</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>19376770.19</v>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0.2718606081952797</v>
+      </c>
+      <c r="C13" s="6">
+        <f>0.2718606081952797+$B$7</f>
+        <v/>
+      </c>
+      <c r="D13" s="6">
+        <f>C13-B13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>periods.current.cogs</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>14108989.66</v>
+        <v>12642673.27</v>
+      </c>
+      <c r="C14" s="5">
+        <f>C12*C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>C14-B14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>periods.current.grossProfit</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>5267780.53</v>
+        <v>8352332.95</v>
+      </c>
+      <c r="C15" s="5">
+        <f>3480138.73+(696027.75*7)*(1+$B$8)</f>
+        <v/>
+      </c>
+      <c r="D15" s="5">
+        <f>C15-B15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>periods.current.operatingExpenses</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>3480138.73</v>
+        <v>3987810.6</v>
+      </c>
+      <c r="C16" s="5">
+        <f>C14-C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="5">
+        <f>C16-B16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>periods.current.netIncome</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1661587.75</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>periods.current.grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>0.2718606082616702</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>periods.current.netMarginPct</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>0.08575153308354315</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior.periodStart</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior.periodEnd</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior.revenue</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>40491815.42</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior.cogs</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>27755136.44</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior.grossProfit</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>12736678.98</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior.operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>9925912.359999999</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior.netIncome</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>2810766.62</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior.grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>0.314549467537803</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior.netMarginPct</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>0.06941567304022843</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior2.periodStart</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior2.periodEnd</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior2.revenue</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>39537774.9</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior2.cogs</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>28435216.93</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior2.grossProfit</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>11102557.97</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior2.operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>8249044.14</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior2.netIncome</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>2899162.56</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior2.grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n">
-        <v>0.2808088719732179</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="27" t="inlineStr">
-        <is>
-          <t>periods.prior2.netMarginPct</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>0.07332639652415061</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.current.periodStart</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.current.periodEnd</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.current.operating</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>760034.3</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.current.investing</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>212852.1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.current.financing</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>-1330991.51</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.current.netCashChange</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>-358105.11</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.current.cashBeginning</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>-243937.55</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.current.cashEnding</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>-602042.66</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.prior.periodStart</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.prior.periodEnd</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.prior.operating</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>1607367.49</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.prior.investing</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>179545.59</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.prior.financing</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>-1432655.18</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.prior.netCashChange</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>354257.9</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.prior.cashBeginning</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>-598195.45</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="27" t="inlineStr">
-        <is>
-          <t>cashFlow.prior.cashEnding</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>-243937.55</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="27" t="inlineStr">
-        <is>
-          <t>forecast.completedMonths</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="27" t="inlineStr">
-        <is>
-          <t>forecast.remainingMonths</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="27" t="inlineStr">
-        <is>
-          <t>forecast.ytdRevenue</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>19376770.19</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>forecast.ytdGrossProfit</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>5267780.53</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="27" t="inlineStr">
-        <is>
-          <t>forecast.ytdOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>3480138.73</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="27" t="inlineStr">
-        <is>
-          <t>forecast.ytdNetIncome</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="n">
-        <v>1661587.75</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="27" t="inlineStr">
-        <is>
-          <t>forecast.avgMonthlyRevenue</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>3875354.04</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="27" t="inlineStr">
-        <is>
-          <t>forecast.avgMonthlyGrossProfit</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>1053556.11</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="27" t="inlineStr">
-        <is>
-          <t>forecast.avgMonthlyOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>696027.75</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="27" t="inlineStr">
-        <is>
-          <t>forecast.avgMonthlyNetIncome</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>332317.55</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="27" t="inlineStr">
-        <is>
-          <t>forecast.yearEndRevenue</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>46504248.46</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="27" t="inlineStr">
-        <is>
-          <t>forecast.yearEndGrossProfit</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>12642673.27</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="27" t="inlineStr">
-        <is>
-          <t>forecast.yearEndOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>8352332.95</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="27" t="inlineStr">
-        <is>
-          <t>forecast.yearEndNetIncome</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="n">
-        <v>3987810.6</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="27" t="inlineStr">
-        <is>
-          <t>forecast.runRateRevenue</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="n">
-        <v>46504248.46</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="27" t="inlineStr">
-        <is>
-          <t>forecast.runRateGrossProfit</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="n">
-        <v>12642673.27</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="27" t="inlineStr">
-        <is>
-          <t>forecast.runRateOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="n">
-        <v>8352332.95</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="27" t="inlineStr">
-        <is>
-          <t>forecast.runRateNetIncome</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="n">
-        <v>3987810.6</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="27" t="inlineStr">
-        <is>
-          <t>forecast.yearEndGrossMarginPct</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="n">
-        <v>0.2718606081952797</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="27" t="inlineStr">
-        <is>
-          <t>forecast.yearEndNetMarginPct</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="n">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Net Margin %</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
         <v>0.08575153307616747</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="27" t="inlineStr">
-        <is>
-          <t>forecast.yearEndCash</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>-1103389.81</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="27" t="inlineStr">
-        <is>
-          <t>forecast.yearEndOperatingCash</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="n">
-        <v>1824082.32</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[0].periodStart</t>
-        </is>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[0].periodEnd</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[0].revenue</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="n">
-        <v>2041295.53</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[0].cogs</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="n">
-        <v>1705779.19</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[0].grossProfit</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="n">
-        <v>335516.34</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[0].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>917633.4300000001</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[0].netIncome</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="n">
-        <v>-582117</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[0].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="n">
-        <v>0.1643644122416709</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[0].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="n">
-        <v>-0.285170369231152</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[0].month</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[1].periodStart</t>
-        </is>
-      </c>
-      <c r="B86" s="13" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[1].periodEnd</t>
-        </is>
-      </c>
-      <c r="B87" s="13" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[1].revenue</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="n">
-        <v>2424157.48</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[1].cogs</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="n">
-        <v>1668995.34</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[1].grossProfit</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="n">
-        <v>755162.14</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[1].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="n">
-        <v>836162.72</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[1].netIncome</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="n">
-        <v>-69968.27</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[1].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="n">
-        <v>0.3115152980902874</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[1].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="n">
-        <v>-0.02886292271738056</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[1].month</t>
-        </is>
-      </c>
-      <c r="B95" s="13" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[2].periodStart</t>
-        </is>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[2].periodEnd</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[2].revenue</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="n">
-        <v>5290349.77</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[2].cogs</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="n">
-        <v>3616852.68</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[2].grossProfit</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="n">
-        <v>1673497.09</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[2].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="n">
-        <v>897079.72</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[2].netIncome</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="n">
-        <v>790908.5600000001</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[2].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="n">
-        <v>0.3163301412488649</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[2].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="n">
-        <v>0.1495002399434925</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[2].month</t>
-        </is>
-      </c>
-      <c r="B105" s="13" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[3].periodStart</t>
-        </is>
-      </c>
-      <c r="B106" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[3].periodEnd</t>
-        </is>
-      </c>
-      <c r="B107" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[3].revenue</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="n">
-        <v>4593904.49</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[3].cogs</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="n">
-        <v>3242912.67</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[3].grossProfit</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="n">
-        <v>1350991.82</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[3].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="n">
-        <v>713341.59</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[3].netIncome</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="n">
-        <v>677429.8100000001</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[3].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="n">
-        <v>0.2940835672445598</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[3].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="n">
-        <v>0.1474627544988424</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="27" t="inlineStr">
-        <is>
-          <t>verifiedMonths[3].month</t>
-        </is>
-      </c>
-      <c r="B115" s="13" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
+      <c r="C17" s="6">
+        <f>C16/C12</f>
+        <v/>
+      </c>
+      <c r="D17" s="6">
+        <f>C17-B17</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/cfo-dashboard/downloads/cfo-dashboard.xlsx
+++ b/cfo-dashboard/downloads/cfo-dashboard.xlsx
@@ -1117,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07T04:02:32.164249+00:00</t>
+          <t>2026-06-18T00:24:51.804946+00:00</t>
         </is>
       </c>
     </row>
@@ -3709,590 +3709,2086 @@
     <row r="241">
       <c r="A241" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].periodStart</t>
-        </is>
-      </c>
-      <c r="B241" s="13" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
+          <t>forecast.currentYear</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].periodEnd</t>
+          <t>projections.methods[0].id</t>
         </is>
       </c>
       <c r="B242" s="13" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>run_rate</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].revenue</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="n">
-        <v>2041295.53</v>
+          <t>projections.methods[0].label</t>
+        </is>
+      </c>
+      <c r="B243" s="13" t="inlineStr">
+        <is>
+          <t>Run-rate (YTD ÷ months × 12)</t>
+        </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].cogs</t>
+          <t>projections.methods[0].yearEnd</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
-        <v>1705779.19</v>
+        <v>46504248.46</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].grossProfit</t>
-        </is>
-      </c>
-      <c r="B245" s="5" t="n">
-        <v>335516.34</v>
+          <t>projections.methods[0].assumption</t>
+        </is>
+      </c>
+      <c r="B245" s="13" t="inlineStr">
+        <is>
+          <t>YTD avg monthly $3,875,354 continues for 7 months</t>
+        </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B246" s="5" t="n">
-        <v>917633.4300000001</v>
+          <t>projections.methods[0].confidence</t>
+        </is>
+      </c>
+      <c r="B246" s="13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].netIncome</t>
-        </is>
-      </c>
-      <c r="B247" s="5" t="n">
-        <v>-582117</v>
+          <t>projections.methods[1].id</t>
+        </is>
+      </c>
+      <c r="B247" s="13" t="inlineStr">
+        <is>
+          <t>yoy_adjusted</t>
+        </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B248" s="6" t="n">
-        <v>0.1643644122416709</v>
+          <t>projections.methods[1].label</t>
+        </is>
+      </c>
+      <c r="B248" s="13" t="inlineStr">
+        <is>
+          <t>YoY growth-adjusted</t>
+        </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B249" s="6" t="n">
-        <v>-0.285170369231152</v>
+          <t>projections.methods[1].yearEnd</t>
+        </is>
+      </c>
+      <c r="B249" s="5" t="n">
+        <v>47158830.4</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].month</t>
+          <t>projections.methods[1].assumption</t>
         </is>
       </c>
       <c r="B250" s="13" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>Apply prior-year YoY growth +2.4% to remaining 7 months</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].periodStart</t>
-        </is>
-      </c>
-      <c r="B251" s="13" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
+          <t>projections.methods[1].yoyGrowth</t>
+        </is>
+      </c>
+      <c r="B251" s="6" t="n">
+        <v>0.02412984854137568</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].periodEnd</t>
+          <t>projections.methods[1].confidence</t>
         </is>
       </c>
       <c r="B252" s="13" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].revenue</t>
-        </is>
-      </c>
-      <c r="B253" s="5" t="n">
-        <v>2424157.48</v>
+          <t>projections.methods[2].id</t>
+        </is>
+      </c>
+      <c r="B253" s="13" t="inlineStr">
+        <is>
+          <t>seasonality_adjusted</t>
+        </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].cogs</t>
-        </is>
-      </c>
-      <c r="B254" s="5" t="n">
-        <v>1668995.34</v>
+          <t>projections.methods[2].label</t>
+        </is>
+      </c>
+      <c r="B254" s="13" t="inlineStr">
+        <is>
+          <t>Seasonality-adjusted (prior-year monthly avg)</t>
+        </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].grossProfit</t>
+          <t>projections.methods[2].yearEnd</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
-        <v>755162.14</v>
+        <v>42996995.85</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B256" s="5" t="n">
-        <v>836162.72</v>
+          <t>projections.methods[2].assumption</t>
+        </is>
+      </c>
+      <c r="B256" s="13" t="inlineStr">
+        <is>
+          <t>YTD actual + prior-year avg monthly $3,374,318 × 7 remaining months</t>
+        </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].netIncome</t>
-        </is>
-      </c>
-      <c r="B257" s="5" t="n">
-        <v>-69968.27</v>
+          <t>projections.methods[2].confidence</t>
+        </is>
+      </c>
+      <c r="B257" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B258" s="6" t="n">
-        <v>0.3115152980902874</v>
+          <t>projections.methods[3].id</t>
+        </is>
+      </c>
+      <c r="B258" s="13" t="inlineStr">
+        <is>
+          <t>pipeline_driven</t>
+        </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B259" s="6" t="n">
-        <v>-0.02886292271738056</v>
+          <t>projections.methods[3].label</t>
+        </is>
+      </c>
+      <c r="B259" s="13" t="inlineStr">
+        <is>
+          <t>Pipeline-driven (open invoices billing cadence)</t>
+        </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].month</t>
-        </is>
-      </c>
-      <c r="B260" s="13" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
+          <t>projections.methods[3].yearEnd</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="n">
+        <v>52919774.6</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].periodStart</t>
-        </is>
-      </c>
-      <c r="B261" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+          <t>projections.methods[3].yearEndBillings</t>
+        </is>
+      </c>
+      <c r="B261" s="5" t="n">
+        <v>44902063.06</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].periodEnd</t>
+          <t>projections.methods[3].assumption</t>
         </is>
       </c>
       <c r="B262" s="13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>Avg billings $4,065,858/mo × 7 remaining + YTD; recognized at YTD billings→revenue ratio of 1.18</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].revenue</t>
+          <t>projections.methods[3].billingsToRevenueRatio</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
-        <v>5290349.77</v>
+        <v>1.178559981161696</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].cogs</t>
+          <t>projections.methods[3].ytdBillings</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
-        <v>3616852.68</v>
+        <v>16441055.61</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].grossProfit</t>
+          <t>projections.methods[3].avgMonthlyBillings</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
-        <v>1673497.09</v>
+        <v>4065858.21</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B266" s="5" t="n">
-        <v>897079.72</v>
+          <t>projections.methods[3].confidence</t>
+        </is>
+      </c>
+      <c r="B266" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].netIncome</t>
+          <t>projections.consensus</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
-        <v>790908.5600000001</v>
+        <v>47394962.33</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B268" s="6" t="n">
-        <v>0.3163301412488649</v>
+          <t>projections.low</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="n">
+        <v>42996995.85</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="n">
-        <v>0.1495002399434925</v>
+          <t>projections.high</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="n">
+        <v>52919774.6</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].month</t>
-        </is>
-      </c>
-      <c r="B270" s="13" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
+          <t>projections.spread</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="n">
+        <v>9922778.75</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].periodStart</t>
-        </is>
-      </c>
-      <c r="B271" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
+          <t>multiYear.anchor.year</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].periodEnd</t>
-        </is>
-      </c>
-      <c r="B272" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
+          <t>multiYear.anchor.revenue</t>
+        </is>
+      </c>
+      <c r="B272" s="5" t="n">
+        <v>46504248.46</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].revenue</t>
-        </is>
-      </c>
-      <c r="B273" s="5" t="n">
-        <v>4593904.49</v>
+          <t>multiYear.anchor.grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B273" s="6" t="n">
+        <v>0.2718606081952797</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].cogs</t>
-        </is>
-      </c>
-      <c r="B274" s="5" t="n">
-        <v>3242912.67</v>
+          <t>multiYear.anchor.netMarginPct</t>
+        </is>
+      </c>
+      <c r="B274" s="6" t="n">
+        <v>0.08575153307616747</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].grossProfit</t>
-        </is>
-      </c>
-      <c r="B275" s="5" t="n">
-        <v>1350991.82</v>
+          <t>multiYear.baseCagr</t>
+        </is>
+      </c>
+      <c r="B275" s="6" t="n">
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B276" s="5" t="n">
-        <v>713341.59</v>
+          <t>multiYear.scenarios.bearish.label</t>
+        </is>
+      </c>
+      <c r="B276" s="13" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].netIncome</t>
-        </is>
-      </c>
-      <c r="B277" s="5" t="n">
-        <v>677429.8100000001</v>
+          <t>multiYear.scenarios.bearish.growth</t>
+        </is>
+      </c>
+      <c r="B277" s="6" t="n">
+        <v>0.0345</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].grossMarginPct</t>
+          <t>multiYear.scenarios.bearish.gmShift</t>
         </is>
       </c>
       <c r="B278" s="6" t="n">
-        <v>0.2940835672445598</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B279" s="6" t="n">
-        <v>0.1474627544988424</v>
+          <t>multiYear.scenarios.bearish.years[0].year</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="n">
+        <v>2027</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].month</t>
-        </is>
-      </c>
-      <c r="B280" s="13" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
+          <t>multiYear.scenarios.bearish.years[0].revenue</t>
+        </is>
+      </c>
+      <c r="B280" s="5" t="n">
+        <v>48109881.41</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="29" t="inlineStr">
         <is>
-          <t>benchmark.companyName</t>
-        </is>
-      </c>
-      <c r="B281" s="13" t="inlineStr">
-        <is>
-          <t>Midwest Design Group LLC</t>
-        </is>
+          <t>multiYear.scenarios.bearish.years[0].grossProfit</t>
+        </is>
+      </c>
+      <c r="B281" s="5" t="n">
+        <v>12116983.99</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="29" t="inlineStr">
         <is>
-          <t>benchmark.metricType</t>
-        </is>
-      </c>
-      <c r="B282" s="13" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
+          <t>multiYear.scenarios.bearish.years[0].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B282" s="6" t="n">
+        <v>0.2518606081952797</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="29" t="inlineStr">
         <is>
-          <t>benchmark.metricLabel</t>
-        </is>
-      </c>
-      <c r="B283" s="13" t="inlineStr">
-        <is>
-          <t>Yearly Profit</t>
-        </is>
+          <t>multiYear.scenarios.bearish.years[0].netIncome</t>
+        </is>
+      </c>
+      <c r="B283" s="5" t="n">
+        <v>3451957.75</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="29" t="inlineStr">
         <is>
-          <t>benchmark.metricValue</t>
-        </is>
-      </c>
-      <c r="B284" s="5" t="n">
-        <v>3757685.49</v>
+          <t>multiYear.scenarios.bearish.years[0].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B284" s="6" t="n">
+        <v>0.07175153307616747</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="29" t="inlineStr">
         <is>
-          <t>benchmark.regionalAverage</t>
+          <t>multiYear.scenarios.bearish.years[1].year</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
-        <v>101486.51</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="29" t="inlineStr">
         <is>
-          <t>benchmark.nationalAverage</t>
-        </is>
-      </c>
-      <c r="B286" s="13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+          <t>multiYear.scenarios.bearish.years[1].revenue</t>
+        </is>
+      </c>
+      <c r="B286" s="5" t="n">
+        <v>49770951.38</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="29" t="inlineStr">
         <is>
-          <t>benchmark.vsRegionalPercent</t>
+          <t>multiYear.scenarios.bearish.years[1].grossProfit</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
-        <v>3602.65</v>
+        <v>11539923.06</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="29" t="inlineStr">
         <is>
-          <t>benchmark.vsNationalPercent</t>
+          <t>multiYear.scenarios.bearish.years[1].grossMarginPct</t>
         </is>
       </c>
       <c r="B288" s="6" t="n">
-        <v>0</v>
+        <v>0.2318606081952797</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="29" t="inlineStr">
         <is>
-          <t>benchmark.isAboveRegional</t>
-        </is>
-      </c>
-      <c r="B289" s="6" t="b">
-        <v>1</v>
+          <t>multiYear.scenarios.bearish.years[1].netIncome</t>
+        </is>
+      </c>
+      <c r="B289" s="5" t="n">
+        <v>2874348.75</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="29" t="inlineStr">
         <is>
-          <t>benchmark.isAboveNational</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="b">
-        <v>0</v>
+          <t>multiYear.scenarios.bearish.years[1].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="n">
+        <v>0.05775153307616747</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="29" t="inlineStr">
         <is>
-          <t>benchmark.location</t>
+          <t>multiYear.scenarios.base.label</t>
         </is>
       </c>
       <c r="B291" s="13" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Base</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="29" t="inlineStr">
         <is>
-          <t>benchmark.naicsCode</t>
-        </is>
-      </c>
-      <c r="B292" s="13" t="inlineStr">
-        <is>
-          <t>236220</t>
-        </is>
+          <t>multiYear.scenarios.base.growth</t>
+        </is>
+      </c>
+      <c r="B292" s="6" t="n">
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="29" t="inlineStr">
         <is>
-          <t>benchmark.industryType</t>
-        </is>
-      </c>
-      <c r="B293" s="13" t="inlineStr">
-        <is>
-          <t>Commercial And Institutional Building Construction</t>
-        </is>
+          <t>multiYear.scenarios.base.gmShift</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="29" t="inlineStr">
         <is>
-          <t>benchmark.benchmarkPeriodRange</t>
-        </is>
-      </c>
-      <c r="B294" s="13" t="inlineStr">
-        <is>
-          <t>Mar 2025 - Feb 2026</t>
-        </is>
+          <t>multiYear.scenarios.base.years[0].year</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="n">
+        <v>2027</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="29" t="inlineStr">
         <is>
+          <t>multiYear.scenarios.base.years[0].revenue</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="n">
+        <v>50435093.83</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.base.years[0].grossProfit</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="n">
+        <v>13711315.28</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.base.years[0].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="n">
+        <v>0.2718606081952797</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.base.years[0].netIncome</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="n">
+        <v>4324886.62</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.base.years[0].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="n">
+        <v>0.08575153307616747</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.base.years[1].year</t>
+        </is>
+      </c>
+      <c r="B300" s="5" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.base.years[1].revenue</t>
+        </is>
+      </c>
+      <c r="B301" s="5" t="n">
+        <v>54698200.15</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.base.years[1].grossProfit</t>
+        </is>
+      </c>
+      <c r="B302" s="5" t="n">
+        <v>14870285.96</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.base.years[1].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B303" s="6" t="n">
+        <v>0.2718606081952797</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.base.years[1].netIncome</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="n">
+        <v>4690454.52</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.base.years[1].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B305" s="6" t="n">
+        <v>0.08575153307616747</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.label</t>
+        </is>
+      </c>
+      <c r="B306" s="13" t="inlineStr">
+        <is>
+          <t>Optimistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.growth</t>
+        </is>
+      </c>
+      <c r="B307" s="6" t="n">
+        <v>0.1245</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.gmShift</t>
+        </is>
+      </c>
+      <c r="B308" s="6" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[0].year</t>
+        </is>
+      </c>
+      <c r="B309" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[0].revenue</t>
+        </is>
+      </c>
+      <c r="B310" s="5" t="n">
+        <v>52295263.77</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[0].grossProfit</t>
+        </is>
+      </c>
+      <c r="B311" s="5" t="n">
+        <v>15001451.17</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[0].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B312" s="6" t="n">
+        <v>0.2868606081952797</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[0].netIncome</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="n">
+        <v>5033499.31</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[0].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B314" s="6" t="n">
+        <v>0.09625153307616746</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[1].year</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[1].revenue</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="n">
+        <v>58807414.45</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[1].grossProfit</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="n">
+        <v>17751641.89</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[1].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B318" s="6" t="n">
+        <v>0.3018606081952797</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[1].netIncome</t>
+        </is>
+      </c>
+      <c r="B319" s="5" t="n">
+        <v>6277781.65</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="29" t="inlineStr">
+        <is>
+          <t>multiYear.scenarios.optimistic.years[1].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B320" s="6" t="n">
+        <v>0.1067515330761675</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.asOf</t>
+        </is>
+      </c>
+      <c r="B321" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.periodStart</t>
+        </is>
+      </c>
+      <c r="B322" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.periodEnd</t>
+        </is>
+      </c>
+      <c r="B323" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.invoiceCount</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.ytdBillings</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="n">
+        <v>16441055.61</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.ytdOpenBalance</t>
+        </is>
+      </c>
+      <c r="B326" s="5" t="n">
+        <v>3518300.82</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.ytdCollected</t>
+        </is>
+      </c>
+      <c r="B327" s="5" t="n">
+        <v>12922754.79</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.openInvoiceCount</t>
+        </is>
+      </c>
+      <c r="B328" s="5" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[0].month</t>
+        </is>
+      </c>
+      <c r="B329" s="13" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[0].billings</t>
+        </is>
+      </c>
+      <c r="B330" s="5" t="n">
+        <v>2732933.77</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[0].openBalance</t>
+        </is>
+      </c>
+      <c r="B331" s="5" t="n">
+        <v>82181.03999999999</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[0].count</t>
+        </is>
+      </c>
+      <c r="B332" s="5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[1].month</t>
+        </is>
+      </c>
+      <c r="B333" s="13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[1].billings</t>
+        </is>
+      </c>
+      <c r="B334" s="5" t="n">
+        <v>3783851.42</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[1].openBalance</t>
+        </is>
+      </c>
+      <c r="B335" s="5" t="n">
+        <v>243933.33</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[1].count</t>
+        </is>
+      </c>
+      <c r="B336" s="5" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[2].month</t>
+        </is>
+      </c>
+      <c r="B337" s="13" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[2].billings</t>
+        </is>
+      </c>
+      <c r="B338" s="5" t="n">
+        <v>4814613.14</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[2].openBalance</t>
+        </is>
+      </c>
+      <c r="B339" s="5" t="n">
+        <v>693136.46</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[2].count</t>
+        </is>
+      </c>
+      <c r="B340" s="5" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[3].month</t>
+        </is>
+      </c>
+      <c r="B341" s="13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[3].billings</t>
+        </is>
+      </c>
+      <c r="B342" s="5" t="n">
+        <v>4932034.5</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[3].openBalance</t>
+        </is>
+      </c>
+      <c r="B343" s="5" t="n">
+        <v>2397076.37</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[3].count</t>
+        </is>
+      </c>
+      <c r="B344" s="5" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[4].month</t>
+        </is>
+      </c>
+      <c r="B345" s="13" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[4].billings</t>
+        </is>
+      </c>
+      <c r="B346" s="5" t="n">
+        <v>177622.78</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[4].openBalance</t>
+        </is>
+      </c>
+      <c r="B347" s="5" t="n">
+        <v>101973.62</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="29" t="inlineStr">
+        <is>
+          <t>pipeline.monthlyBillings[4].count</t>
+        </is>
+      </c>
+      <c r="B348" s="5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="29" t="inlineStr">
+        <is>
+          <t>customers.period</t>
+        </is>
+      </c>
+      <c r="B349" s="13" t="inlineStr">
+        <is>
+          <t>THIS_YEAR_TO_DATE_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="29" t="inlineStr">
+        <is>
+          <t>customers.totalSales</t>
+        </is>
+      </c>
+      <c r="B350" s="5" t="n">
+        <v>75418579.22000004</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="29" t="inlineStr">
+        <is>
+          <t>customers.customerCount</t>
+        </is>
+      </c>
+      <c r="B351" s="5" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="29" t="inlineStr">
+        <is>
+          <t>customers.top5Concentration</t>
+        </is>
+      </c>
+      <c r="B352" s="5" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[0].name</t>
+        </is>
+      </c>
+      <c r="B353" s="13" t="inlineStr">
+        <is>
+          <t>Thompson Thrift Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[0].sales</t>
+        </is>
+      </c>
+      <c r="B354" s="5" t="n">
+        <v>2717218.65</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[0].percent</t>
+        </is>
+      </c>
+      <c r="B355" s="5" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[1].name</t>
+        </is>
+      </c>
+      <c r="B356" s="13" t="inlineStr">
+        <is>
+          <t>MF.2025.972 Union Flats - Fishers</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[1].sales</t>
+        </is>
+      </c>
+      <c r="B357" s="5" t="n">
+        <v>2717218.65</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[1].percent</t>
+        </is>
+      </c>
+      <c r="B358" s="5" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[2].name</t>
+        </is>
+      </c>
+      <c r="B359" s="13" t="inlineStr">
+        <is>
+          <t>The Peterson Company, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[2].sales</t>
+        </is>
+      </c>
+      <c r="B360" s="5" t="n">
+        <v>2587643.01</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[2].percent</t>
+        </is>
+      </c>
+      <c r="B361" s="5" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[3].name</t>
+        </is>
+      </c>
+      <c r="B362" s="13" t="inlineStr">
+        <is>
+          <t>DEEM, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[3].sales</t>
+        </is>
+      </c>
+      <c r="B363" s="5" t="n">
+        <v>2041679.82</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[3].percent</t>
+        </is>
+      </c>
+      <c r="B364" s="5" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[4].name</t>
+        </is>
+      </c>
+      <c r="B365" s="13" t="inlineStr">
+        <is>
+          <t>Marous Brothers Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[4].sales</t>
+        </is>
+      </c>
+      <c r="B366" s="5" t="n">
+        <v>2039464.17</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[4].percent</t>
+        </is>
+      </c>
+      <c r="B367" s="5" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[5].name</t>
+        </is>
+      </c>
+      <c r="B368" s="13" t="inlineStr">
+        <is>
+          <t>MF.2025.1019 Town &amp; Country Apartments (NY MF Project - 22 bldgs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[5].sales</t>
+        </is>
+      </c>
+      <c r="B369" s="5" t="n">
+        <v>2039464.17</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[5].percent</t>
+        </is>
+      </c>
+      <c r="B370" s="5" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[6].name</t>
+        </is>
+      </c>
+      <c r="B371" s="13" t="inlineStr">
+        <is>
+          <t>Skender Construction of Indiana LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[6].sales</t>
+        </is>
+      </c>
+      <c r="B372" s="5" t="n">
+        <v>2035601.3</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[6].percent</t>
+        </is>
+      </c>
+      <c r="B373" s="5" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[7].name</t>
+        </is>
+      </c>
+      <c r="B374" s="13" t="inlineStr">
+        <is>
+          <t>MILHAUS Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[7].sales</t>
+        </is>
+      </c>
+      <c r="B375" s="5" t="n">
+        <v>1886647.5</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[7].percent</t>
+        </is>
+      </c>
+      <c r="B376" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[8].name</t>
+        </is>
+      </c>
+      <c r="B377" s="13" t="inlineStr">
+        <is>
+          <t>Compass Commercial Construction Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[8].sales</t>
+        </is>
+      </c>
+      <c r="B378" s="5" t="n">
+        <v>1704370.92</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[8].percent</t>
+        </is>
+      </c>
+      <c r="B379" s="5" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[9].name</t>
+        </is>
+      </c>
+      <c r="B380" s="13" t="inlineStr">
+        <is>
+          <t>2025.964 Avon Municipal Building</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[9].sales</t>
+        </is>
+      </c>
+      <c r="B381" s="5" t="n">
+        <v>1361655.46</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="29" t="inlineStr">
+        <is>
+          <t>customers.topCustomers[9].percent</t>
+        </is>
+      </c>
+      <c r="B382" s="5" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].periodStart</t>
+        </is>
+      </c>
+      <c r="B383" s="13" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].periodEnd</t>
+        </is>
+      </c>
+      <c r="B384" s="13" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].revenue</t>
+        </is>
+      </c>
+      <c r="B385" s="5" t="n">
+        <v>2041295.53</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].cogs</t>
+        </is>
+      </c>
+      <c r="B386" s="5" t="n">
+        <v>1705779.19</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].grossProfit</t>
+        </is>
+      </c>
+      <c r="B387" s="5" t="n">
+        <v>335516.34</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B388" s="5" t="n">
+        <v>917633.4300000001</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].netIncome</t>
+        </is>
+      </c>
+      <c r="B389" s="5" t="n">
+        <v>-582117</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B390" s="6" t="n">
+        <v>0.1643644122416709</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B391" s="6" t="n">
+        <v>-0.285170369231152</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[0].month</t>
+        </is>
+      </c>
+      <c r="B392" s="13" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].periodStart</t>
+        </is>
+      </c>
+      <c r="B393" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].periodEnd</t>
+        </is>
+      </c>
+      <c r="B394" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].revenue</t>
+        </is>
+      </c>
+      <c r="B395" s="5" t="n">
+        <v>2424157.48</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].cogs</t>
+        </is>
+      </c>
+      <c r="B396" s="5" t="n">
+        <v>1668995.34</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].grossProfit</t>
+        </is>
+      </c>
+      <c r="B397" s="5" t="n">
+        <v>755162.14</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B398" s="5" t="n">
+        <v>836162.72</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].netIncome</t>
+        </is>
+      </c>
+      <c r="B399" s="5" t="n">
+        <v>-69968.27</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B400" s="6" t="n">
+        <v>0.3115152980902874</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B401" s="6" t="n">
+        <v>-0.02886292271738056</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[1].month</t>
+        </is>
+      </c>
+      <c r="B402" s="13" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].periodStart</t>
+        </is>
+      </c>
+      <c r="B403" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].periodEnd</t>
+        </is>
+      </c>
+      <c r="B404" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].revenue</t>
+        </is>
+      </c>
+      <c r="B405" s="5" t="n">
+        <v>5290349.77</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].cogs</t>
+        </is>
+      </c>
+      <c r="B406" s="5" t="n">
+        <v>3616852.68</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].grossProfit</t>
+        </is>
+      </c>
+      <c r="B407" s="5" t="n">
+        <v>1673497.09</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B408" s="5" t="n">
+        <v>897079.72</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].netIncome</t>
+        </is>
+      </c>
+      <c r="B409" s="5" t="n">
+        <v>790908.5600000001</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B410" s="6" t="n">
+        <v>0.3163301412488649</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B411" s="6" t="n">
+        <v>0.1495002399434925</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[2].month</t>
+        </is>
+      </c>
+      <c r="B412" s="13" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].periodStart</t>
+        </is>
+      </c>
+      <c r="B413" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].periodEnd</t>
+        </is>
+      </c>
+      <c r="B414" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].revenue</t>
+        </is>
+      </c>
+      <c r="B415" s="5" t="n">
+        <v>4593904.49</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].cogs</t>
+        </is>
+      </c>
+      <c r="B416" s="5" t="n">
+        <v>3242912.67</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].grossProfit</t>
+        </is>
+      </c>
+      <c r="B417" s="5" t="n">
+        <v>1350991.82</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B418" s="5" t="n">
+        <v>713341.59</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].netIncome</t>
+        </is>
+      </c>
+      <c r="B419" s="5" t="n">
+        <v>677429.8100000001</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B420" s="6" t="n">
+        <v>0.2940835672445598</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B421" s="6" t="n">
+        <v>0.1474627544988424</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[3].month</t>
+        </is>
+      </c>
+      <c r="B422" s="13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.companyName</t>
+        </is>
+      </c>
+      <c r="B423" s="13" t="inlineStr">
+        <is>
+          <t>Midwest Design Group LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricType</t>
+        </is>
+      </c>
+      <c r="B424" s="13" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricLabel</t>
+        </is>
+      </c>
+      <c r="B425" s="13" t="inlineStr">
+        <is>
+          <t>Yearly Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricValue</t>
+        </is>
+      </c>
+      <c r="B426" s="5" t="n">
+        <v>3757685.49</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.regionalAverage</t>
+        </is>
+      </c>
+      <c r="B427" s="5" t="n">
+        <v>101486.51</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.nationalAverage</t>
+        </is>
+      </c>
+      <c r="B428" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.vsRegionalPercent</t>
+        </is>
+      </c>
+      <c r="B429" s="5" t="n">
+        <v>3602.65</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.vsNationalPercent</t>
+        </is>
+      </c>
+      <c r="B430" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.isAboveRegional</t>
+        </is>
+      </c>
+      <c r="B431" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.isAboveNational</t>
+        </is>
+      </c>
+      <c r="B432" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.location</t>
+        </is>
+      </c>
+      <c r="B433" s="13" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.naicsCode</t>
+        </is>
+      </c>
+      <c r="B434" s="13" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.industryType</t>
+        </is>
+      </c>
+      <c r="B435" s="13" t="inlineStr">
+        <is>
+          <t>Commercial And Institutional Building Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.benchmarkPeriodRange</t>
+        </is>
+      </c>
+      <c r="B436" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2025 - Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="29" t="inlineStr">
+        <is>
           <t>benchmark.reportDate</t>
         </is>
       </c>
-      <c r="B295" s="13" t="inlineStr">
+      <c r="B437" s="13" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>

--- a/cfo-dashboard/downloads/cfo-dashboard.xlsx
+++ b/cfo-dashboard/downloads/cfo-dashboard.xlsx
@@ -208,12 +208,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -221,6 +215,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -612,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Commercial and Institutional Building Construction (NAICS 236220)  ·  As of 2026-05-07  ·  Source: QuickBooks Online (live, via QuickBooks MCP)</t>
+          <t>Commercial and Institutional Building Construction (NAICS 236220)  ·  As of 2026-06-30  ·  Source: QuickBooks Online (live, via QuickBooks MCP)</t>
         </is>
       </c>
     </row>
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30132990.57</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
       <c r="D5" s="5">
         <f>B5-C5</f>
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5267780.53</v>
+        <v>10042858.2</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>12736678.98</v>
+        <v>12737250.31</v>
       </c>
       <c r="D6" s="5">
         <f>B6-C6</f>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.2718606082616702</v>
+        <v>0.3332844835520087</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.314549467537803</v>
+        <v>0.3145635773804887</v>
       </c>
       <c r="D7" s="6">
         <f>B7-C7</f>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5242172.32</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>9925912.359999999</v>
+        <v>9926483.689999999</v>
       </c>
       <c r="D8" s="5">
         <f>B8-C8</f>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4800685.88</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>2810766.62</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.08575153308354315</v>
+        <v>0.15931660911146</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.06941567304022843</v>
+        <v>0.06941567305737158</v>
       </c>
       <c r="D10" s="6">
         <f>B10-C10</f>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>-602042.66</v>
+        <v>-892004.02</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>-243937.55</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>760034.3</v>
+        <v>856166.26</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>1607367.49</v>
@@ -874,7 +874,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Commercial And Institutional Building Construction  ·  NAICS 236220  ·  IN  ·  Mar 2025 - Feb 2026</t>
+          <t>Commercial And Institutional Building Construction  ·  NAICS 236220  ·  IN  ·  May 2025 - Apr 2026</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3757685.49</v>
+        <v>5328445.58</v>
       </c>
     </row>
     <row r="6">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>101486.51</v>
+        <v>76856.14999999999</v>
       </c>
     </row>
     <row r="7">
@@ -947,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1010,95 +1010,117 @@
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t>Run-rate $46,504,248 vs FY 2025 $40,491,815.</t>
+          <t>Run-rate $60,265,981 vs FY 2025 $40,491,815.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>Gross margin compression vs prior year</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>BAD</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Gross margin expansion vs prior year</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
-        <is>
-          <t>GM% 27.19% vs prior 31.45% (-4.27pt).</t>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>GM% 33.33% vs prior 31.46% (+1.87pt).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
+          <t>Operating expense run-rate above prior year</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>OpEx run-rate $10,484,345 vs prior $9,926,484 (+5.6%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
           <t>Negative net cash flow YTD</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>BAD</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
-        <is>
-          <t>YTD net cash $-358,105 (Op $760,034 + Inv $212,852 + Fin $-1,330,992).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>YTD net cash $-648,066 (Op $856,166 + Inv $212,852 + Fin $-1,717,085).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Negative cash position</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>BAD</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>Cash at end of period $-602,043 (LoC drawn). Beginning $-243,938.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>Cash at end of period $-892,004 (LoC drawn). Beginning $-243,938.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>A/R collection risk</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
-        <is>
-          <t>Cash deteriorated by $-358,105 vs prior year-end.</t>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>Cash deteriorated by $-648,066 vs prior year-end.</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1206,7 +1228,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1240,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18T00:24:51.804946+00:00</t>
+          <t>2026-07-02T15:48:54.949750+00:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1756,7 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1767,7 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30132990.57</v>
       </c>
     </row>
     <row r="55">
@@ -1755,7 +1777,7 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>14108989.66</v>
+        <v>20090132.37</v>
       </c>
     </row>
     <row r="56">
@@ -1765,7 +1787,7 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>5267780.53</v>
+        <v>10042858.2</v>
       </c>
     </row>
     <row r="57">
@@ -1775,7 +1797,7 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5242172.32</v>
       </c>
     </row>
     <row r="58">
@@ -1785,7 +1807,7 @@
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4800685.88</v>
       </c>
     </row>
     <row r="59">
@@ -1795,7 +1817,7 @@
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>0.2718606082616702</v>
+        <v>0.3332844835520087</v>
       </c>
     </row>
     <row r="60">
@@ -1805,7 +1827,7 @@
         </is>
       </c>
       <c r="B60" s="6" t="n">
-        <v>0.08575153308354315</v>
+        <v>0.15931660911146</v>
       </c>
     </row>
     <row r="61">
@@ -1849,7 +1871,7 @@
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>571765.41</v>
+        <v>954478.7</v>
       </c>
     </row>
     <row r="65">
@@ -1871,7 +1893,7 @@
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>16823.83</v>
+        <v>16826.61</v>
       </c>
     </row>
     <row r="67">
@@ -1893,7 +1915,7 @@
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>206725</v>
+        <v>396425</v>
       </c>
     </row>
     <row r="69">
@@ -1937,7 +1959,7 @@
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>15924134.62</v>
+        <v>25713723.99</v>
       </c>
     </row>
     <row r="73">
@@ -1959,7 +1981,7 @@
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>2347599</v>
+        <v>2544448.44</v>
       </c>
     </row>
     <row r="75">
@@ -1981,7 +2003,7 @@
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>6261029.85</v>
+        <v>8677589.449999999</v>
       </c>
     </row>
     <row r="77">
@@ -2003,7 +2025,7 @@
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>2745051.1</v>
+        <v>3879854.77</v>
       </c>
     </row>
     <row r="79">
@@ -2025,7 +2047,7 @@
         </is>
       </c>
       <c r="B80" s="5" t="n">
-        <v>529849.5</v>
+        <v>781598.96</v>
       </c>
     </row>
     <row r="81">
@@ -2047,7 +2069,7 @@
         </is>
       </c>
       <c r="B82" s="5" t="n">
-        <v>1928101.09</v>
+        <v>2916068.14</v>
       </c>
     </row>
     <row r="83">
@@ -2069,7 +2091,7 @@
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>757455.8100000001</v>
+        <v>990801.9300000001</v>
       </c>
     </row>
     <row r="85">
@@ -2091,7 +2113,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>72850.52</v>
+        <v>139047.64</v>
       </c>
     </row>
     <row r="87">
@@ -2113,7 +2135,7 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>191337.16</v>
+        <v>317740.36</v>
       </c>
     </row>
     <row r="89">
@@ -2135,7 +2157,7 @@
         </is>
       </c>
       <c r="B90" s="5" t="n">
-        <v>64541.24</v>
+        <v>134589.28</v>
       </c>
     </row>
     <row r="91">
@@ -2157,7 +2179,7 @@
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>221218.59</v>
+        <v>402320.28</v>
       </c>
     </row>
     <row r="93">
@@ -2191,7 +2213,7 @@
         </is>
       </c>
       <c r="B95" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
     </row>
     <row r="96">
@@ -2201,7 +2223,7 @@
         </is>
       </c>
       <c r="B96" s="5" t="n">
-        <v>27755136.44</v>
+        <v>27754565.1</v>
       </c>
     </row>
     <row r="97">
@@ -2211,7 +2233,7 @@
         </is>
       </c>
       <c r="B97" s="5" t="n">
-        <v>12736678.98</v>
+        <v>12737250.31</v>
       </c>
     </row>
     <row r="98">
@@ -2221,7 +2243,7 @@
         </is>
       </c>
       <c r="B98" s="5" t="n">
-        <v>9925912.359999999</v>
+        <v>9926483.689999999</v>
       </c>
     </row>
     <row r="99">
@@ -2241,7 +2263,7 @@
         </is>
       </c>
       <c r="B100" s="6" t="n">
-        <v>0.314549467537803</v>
+        <v>0.3145635773804887</v>
       </c>
     </row>
     <row r="101">
@@ -2251,7 +2273,7 @@
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>0.06941567304022843</v>
+        <v>0.06941567305737158</v>
       </c>
     </row>
     <row r="102">
@@ -2537,7 +2559,7 @@
         </is>
       </c>
       <c r="B127" s="5" t="n">
-        <v>33721642.66</v>
+        <v>33721642.65</v>
       </c>
     </row>
     <row r="128">
@@ -2713,7 +2735,7 @@
         </is>
       </c>
       <c r="B143" s="5" t="n">
-        <v>1286006.54</v>
+        <v>196030.17</v>
       </c>
     </row>
     <row r="144">
@@ -2801,7 +2823,7 @@
         </is>
       </c>
       <c r="B151" s="5" t="n">
-        <v>981759.21</v>
+        <v>981248.3100000001</v>
       </c>
     </row>
     <row r="152">
@@ -2918,7 +2940,7 @@
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2951,7 @@
         </is>
       </c>
       <c r="B163" s="5" t="n">
-        <v>760034.3</v>
+        <v>856166.26</v>
       </c>
     </row>
     <row r="164">
@@ -2949,7 +2971,7 @@
         </is>
       </c>
       <c r="B165" s="5" t="n">
-        <v>-1330991.51</v>
+        <v>-1717084.83</v>
       </c>
     </row>
     <row r="166">
@@ -2959,7 +2981,7 @@
         </is>
       </c>
       <c r="B166" s="5" t="n">
-        <v>-358105.11</v>
+        <v>-648066.47</v>
       </c>
     </row>
     <row r="167">
@@ -2979,7 +3001,7 @@
         </is>
       </c>
       <c r="B168" s="5" t="n">
-        <v>-602042.66</v>
+        <v>-892004.02</v>
       </c>
     </row>
     <row r="169">
@@ -2989,7 +3011,7 @@
         </is>
       </c>
       <c r="B169" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4675143.6</v>
       </c>
     </row>
     <row r="170">
@@ -2999,7 +3021,7 @@
         </is>
       </c>
       <c r="B170" s="5" t="n">
-        <v>286831.19</v>
+        <v>933211.54</v>
       </c>
     </row>
     <row r="171">
@@ -3009,7 +3031,7 @@
         </is>
       </c>
       <c r="B171" s="5" t="n">
-        <v>-649262.0699999999</v>
+        <v>-1802279.03</v>
       </c>
     </row>
     <row r="172">
@@ -3019,7 +3041,7 @@
         </is>
       </c>
       <c r="B172" s="5" t="n">
-        <v>-837450.48</v>
+        <v>-1178924.86</v>
       </c>
     </row>
     <row r="173">
@@ -3029,7 +3051,7 @@
         </is>
       </c>
       <c r="B173" s="5" t="n">
-        <v>193111.88</v>
+        <v>84158.12</v>
       </c>
     </row>
     <row r="174">
@@ -3039,7 +3061,7 @@
         </is>
       </c>
       <c r="B174" s="5" t="n">
-        <v>-1073267.83</v>
+        <v>-563772.95</v>
       </c>
     </row>
     <row r="175">
@@ -3049,7 +3071,7 @@
         </is>
       </c>
       <c r="B175" s="5" t="n">
-        <v>-1274331.17</v>
+        <v>-1980675.49</v>
       </c>
     </row>
     <row r="176">
@@ -3059,7 +3081,7 @@
         </is>
       </c>
       <c r="B176" s="5" t="n">
-        <v>224000</v>
+        <v>336000</v>
       </c>
     </row>
     <row r="177">
@@ -3069,2728 +3091,3766 @@
         </is>
       </c>
       <c r="B177" s="5" t="n">
-        <v>-149000</v>
+        <v>-94000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.current.workingCapital.lineOfCreditDraw</t>
+          <t>cashFlow.current.workingCapital.accruedCommissionsChange</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
-        <v>2536373.04</v>
+        <v>-39048.85</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.current.workingCapital.lineOfCreditCapXChange</t>
+          <t>cashFlow.current.workingCapital.lineOfCreditDraw</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
-        <v>-27802.23</v>
+        <v>545048.77</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.periodStart</t>
-        </is>
-      </c>
-      <c r="B180" s="13" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
+          <t>cashFlow.current.workingCapital.lineOfCreditCapXChange</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="n">
+        <v>-27802.23</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.periodEnd</t>
+          <t>cashFlow.prior.periodStart</t>
         </is>
       </c>
       <c r="B181" s="13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.operating</t>
-        </is>
-      </c>
-      <c r="B182" s="5" t="n">
-        <v>1607367.49</v>
+          <t>cashFlow.prior.periodEnd</t>
+        </is>
+      </c>
+      <c r="B182" s="13" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.investing</t>
+          <t>cashFlow.prior.operating</t>
         </is>
       </c>
       <c r="B183" s="5" t="n">
-        <v>179545.59</v>
+        <v>1607367.49</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.financing</t>
+          <t>cashFlow.prior.investing</t>
         </is>
       </c>
       <c r="B184" s="5" t="n">
-        <v>-1432655.18</v>
+        <v>179545.59</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.netCashChange</t>
+          <t>cashFlow.prior.financing</t>
         </is>
       </c>
       <c r="B185" s="5" t="n">
-        <v>354257.9</v>
+        <v>-1432655.18</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.cashBeginning</t>
+          <t>cashFlow.prior.netCashChange</t>
         </is>
       </c>
       <c r="B186" s="5" t="n">
-        <v>-598195.45</v>
+        <v>354257.9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.cashEnding</t>
+          <t>cashFlow.prior.cashBeginning</t>
         </is>
       </c>
       <c r="B187" s="5" t="n">
-        <v>-243937.55</v>
+        <v>-598195.45</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.netIncome</t>
+          <t>cashFlow.prior.cashEnding</t>
         </is>
       </c>
       <c r="B188" s="5" t="n">
-        <v>2810766.62</v>
+        <v>-243937.55</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.accountsPayableChange</t>
+          <t>cashFlow.prior.netIncome</t>
         </is>
       </c>
       <c r="B189" s="5" t="n">
-        <v>712464.46</v>
+        <v>2810766.62</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.accountsReceivableChange</t>
+          <t>cashFlow.prior.workingCapital.accountsPayableChange</t>
         </is>
       </c>
       <c r="B190" s="5" t="n">
-        <v>-733947.11</v>
+        <v>712464.46</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.retainageReceivableChange</t>
+          <t>cashFlow.prior.workingCapital.accountsReceivableChange</t>
         </is>
       </c>
       <c r="B191" s="5" t="n">
-        <v>-2438809.88</v>
+        <v>-733947.11</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.inventoryDrywallChange</t>
+          <t>cashFlow.prior.workingCapital.retainageReceivableChange</t>
         </is>
       </c>
       <c r="B192" s="5" t="n">
-        <v>362396.12</v>
+        <v>-2438809.88</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.wipOverbillingsChange</t>
+          <t>cashFlow.prior.workingCapital.inventoryDrywallChange</t>
         </is>
       </c>
       <c r="B193" s="5" t="n">
-        <v>1249606.34</v>
+        <v>362396.12</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.wipUnderbillingsChange</t>
+          <t>cashFlow.prior.workingCapital.wipOverbillingsChange</t>
         </is>
       </c>
       <c r="B194" s="5" t="n">
-        <v>215079.93</v>
+        <v>1249606.34</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.accruedBonusesChange</t>
+          <t>cashFlow.prior.workingCapital.wipUnderbillingsChange</t>
         </is>
       </c>
       <c r="B195" s="5" t="n">
-        <v>-9352.09</v>
+        <v>215079.93</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.accruedPayrollChange</t>
+          <t>cashFlow.prior.workingCapital.accruedBonusesChange</t>
         </is>
       </c>
       <c r="B196" s="5" t="n">
-        <v>11000</v>
+        <v>-9352.09</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.accruedCommissionsChange</t>
+          <t>cashFlow.prior.workingCapital.accruedPayrollChange</t>
         </is>
       </c>
       <c r="B197" s="5" t="n">
-        <v>-37000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.lineOfCreditDraw</t>
+          <t>cashFlow.prior.workingCapital.accruedCommissionsChange</t>
         </is>
       </c>
       <c r="B198" s="5" t="n">
-        <v>-460964.34</v>
+        <v>-37000</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.lineOfCreditCapXChange</t>
+          <t>cashFlow.prior.workingCapital.lineOfCreditDraw</t>
         </is>
       </c>
       <c r="B199" s="5" t="n">
-        <v>-67265.75999999999</v>
+        <v>-460964.34</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.leaseLiabilityCurrentChange</t>
+          <t>cashFlow.prior.workingCapital.lineOfCreditCapXChange</t>
         </is>
       </c>
       <c r="B200" s="5" t="n">
-        <v>-112868</v>
+        <v>-67265.75999999999</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.leaseLiabilityNoncurrentChange</t>
+          <t>cashFlow.prior.workingCapital.leaseLiabilityCurrentChange</t>
         </is>
       </c>
       <c r="B201" s="5" t="n">
-        <v>-959670</v>
+        <v>-112868</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="29" t="inlineStr">
         <is>
-          <t>cashFlow.prior.workingCapital.rouAssetOperatingLeasesChange</t>
+          <t>cashFlow.prior.workingCapital.leaseLiabilityNoncurrentChange</t>
         </is>
       </c>
       <c r="B202" s="5" t="n">
-        <v>967660</v>
+        <v>-959670</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.current.ar</t>
+          <t>cashFlow.prior.workingCapital.rouAssetOperatingLeasesChange</t>
         </is>
       </c>
       <c r="B203" s="5" t="n">
-        <v>-649262.0699999999</v>
+        <v>967660</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.current.ap</t>
+          <t>workingCapital.current.ar</t>
         </is>
       </c>
       <c r="B204" s="5" t="n">
-        <v>286831.19</v>
+        <v>-1802279.03</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.current.retainage</t>
+          <t>workingCapital.current.ap</t>
         </is>
       </c>
       <c r="B205" s="5" t="n">
-        <v>-837450.48</v>
+        <v>933211.54</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.current.inventory</t>
+          <t>workingCapital.current.retainage</t>
         </is>
       </c>
       <c r="B206" s="5" t="n">
-        <v>193111.88</v>
+        <v>-1178924.86</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.current.wipOverbillings</t>
+          <t>workingCapital.current.inventory</t>
         </is>
       </c>
       <c r="B207" s="5" t="n">
-        <v>-1073267.83</v>
+        <v>84158.12</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.current.wipUnderbillings</t>
+          <t>workingCapital.current.wipOverbillings</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
-        <v>-1274331.17</v>
+        <v>-563772.95</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.current.lineOfCreditDraw</t>
+          <t>workingCapital.current.wipUnderbillings</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
-        <v>2536373.04</v>
+        <v>-1980675.49</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.current.totalWorkingCapitalChange</t>
+          <t>workingCapital.current.lineOfCreditDraw</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
-        <v>-3354368.48</v>
+        <v>545048.77</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.prior.ar</t>
+          <t>workingCapital.current.totalWorkingCapitalChange</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
-        <v>-733947.11</v>
+        <v>-4508282.67</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.prior.ap</t>
+          <t>workingCapital.prior.ar</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
-        <v>712464.46</v>
+        <v>-733947.11</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.prior.retainage</t>
+          <t>workingCapital.prior.ap</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
-        <v>-2438809.88</v>
+        <v>712464.46</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.prior.inventory</t>
+          <t>workingCapital.prior.retainage</t>
         </is>
       </c>
       <c r="B214" s="5" t="n">
-        <v>362396.12</v>
+        <v>-2438809.88</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.prior.wipOverbillings</t>
+          <t>workingCapital.prior.inventory</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
-        <v>1249606.34</v>
+        <v>362396.12</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.prior.wipUnderbillings</t>
+          <t>workingCapital.prior.wipOverbillings</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
-        <v>215079.93</v>
+        <v>1249606.34</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.prior.lineOfCreditDraw</t>
+          <t>workingCapital.prior.wipUnderbillings</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
-        <v>-460964.34</v>
+        <v>215079.93</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="29" t="inlineStr">
         <is>
-          <t>workingCapital.prior.totalWorkingCapitalChange</t>
+          <t>workingCapital.prior.lineOfCreditDraw</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
-        <v>-633210.1399999997</v>
+        <v>-460964.34</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="29" t="inlineStr">
         <is>
-          <t>forecast.completedMonths</t>
+          <t>workingCapital.prior.totalWorkingCapitalChange</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
-        <v>5</v>
+        <v>-633210.1399999997</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="29" t="inlineStr">
         <is>
-          <t>forecast.remainingMonths</t>
+          <t>forecast.completedMonths</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="29" t="inlineStr">
         <is>
-          <t>forecast.ytdRevenue</t>
+          <t>forecast.remainingMonths</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
-        <v>19376770.19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="29" t="inlineStr">
         <is>
-          <t>forecast.ytdGrossProfit</t>
+          <t>forecast.ytdRevenue</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
-        <v>5267780.53</v>
+        <v>30132990.57</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="29" t="inlineStr">
         <is>
-          <t>forecast.ytdOperatingExpenses</t>
+          <t>forecast.ytdGrossProfit</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
-        <v>3480138.73</v>
+        <v>10042858.2</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="29" t="inlineStr">
         <is>
-          <t>forecast.ytdNetIncome</t>
+          <t>forecast.ytdOperatingExpenses</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
-        <v>1661587.75</v>
+        <v>5242172.32</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="29" t="inlineStr">
         <is>
-          <t>forecast.avgMonthlyRevenue</t>
+          <t>forecast.ytdNetIncome</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
-        <v>3875354.04</v>
+        <v>4800685.88</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="29" t="inlineStr">
         <is>
-          <t>forecast.avgMonthlyGrossProfit</t>
+          <t>forecast.avgMonthlyRevenue</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
-        <v>1053556.11</v>
+        <v>5022165.09</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="29" t="inlineStr">
         <is>
-          <t>forecast.avgMonthlyOperatingExpenses</t>
+          <t>forecast.avgMonthlyGrossProfit</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
-        <v>696027.75</v>
+        <v>1673809.7</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="29" t="inlineStr">
         <is>
-          <t>forecast.avgMonthlyNetIncome</t>
+          <t>forecast.avgMonthlyOperatingExpenses</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
-        <v>332317.55</v>
+        <v>873695.39</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="29" t="inlineStr">
         <is>
-          <t>forecast.yearEndRevenue</t>
+          <t>forecast.avgMonthlyNetIncome</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
-        <v>46504248.46</v>
+        <v>800114.3100000001</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="29" t="inlineStr">
         <is>
-          <t>forecast.yearEndGrossProfit</t>
+          <t>forecast.yearEndRevenue</t>
         </is>
       </c>
       <c r="B230" s="5" t="n">
-        <v>12642673.27</v>
+        <v>60265981.14</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="29" t="inlineStr">
         <is>
-          <t>forecast.yearEndOperatingExpenses</t>
+          <t>forecast.yearEndGrossProfit</t>
         </is>
       </c>
       <c r="B231" s="5" t="n">
-        <v>8352332.95</v>
+        <v>20085716.4</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="29" t="inlineStr">
         <is>
-          <t>forecast.yearEndNetIncome</t>
+          <t>forecast.yearEndOperatingExpenses</t>
         </is>
       </c>
       <c r="B232" s="5" t="n">
-        <v>3987810.6</v>
+        <v>10484344.64</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="29" t="inlineStr">
         <is>
-          <t>forecast.runRateRevenue</t>
+          <t>forecast.yearEndNetIncome</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
-        <v>46504248.46</v>
+        <v>9601371.76</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="29" t="inlineStr">
         <is>
-          <t>forecast.runRateGrossProfit</t>
+          <t>forecast.runRateRevenue</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
-        <v>12642673.27</v>
+        <v>60265981.14</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="29" t="inlineStr">
         <is>
-          <t>forecast.runRateOperatingExpenses</t>
+          <t>forecast.runRateGrossProfit</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
-        <v>8352332.95</v>
+        <v>20085716.4</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="29" t="inlineStr">
         <is>
-          <t>forecast.runRateNetIncome</t>
+          <t>forecast.runRateOperatingExpenses</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
-        <v>3987810.6</v>
+        <v>10484344.64</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="29" t="inlineStr">
         <is>
-          <t>forecast.yearEndGrossMarginPct</t>
-        </is>
-      </c>
-      <c r="B237" s="6" t="n">
-        <v>0.2718606081952797</v>
+          <t>forecast.runRateNetIncome</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="n">
+        <v>9601371.76</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="29" t="inlineStr">
         <is>
-          <t>forecast.yearEndNetMarginPct</t>
+          <t>forecast.yearEndGrossMarginPct</t>
         </is>
       </c>
       <c r="B238" s="6" t="n">
-        <v>0.08575153307616747</v>
+        <v>0.3332844835520087</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="29" t="inlineStr">
         <is>
-          <t>forecast.yearEndCash</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="n">
-        <v>-1103389.81</v>
+          <t>forecast.yearEndNetMarginPct</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="n">
+        <v>0.15931660911146</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="29" t="inlineStr">
         <is>
-          <t>forecast.yearEndOperatingCash</t>
+          <t>forecast.yearEndCash</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
-        <v>1824082.32</v>
+        <v>-1540070.49</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="29" t="inlineStr">
         <is>
-          <t>forecast.currentYear</t>
+          <t>forecast.yearEndOperatingCash</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
-        <v>2026</v>
+        <v>1712332.52</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[0].id</t>
-        </is>
-      </c>
-      <c r="B242" s="13" t="inlineStr">
-        <is>
-          <t>run_rate</t>
-        </is>
+          <t>forecast.currentYear</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[0].label</t>
+          <t>projections.methods[0].id</t>
         </is>
       </c>
       <c r="B243" s="13" t="inlineStr">
         <is>
-          <t>Run-rate (YTD ÷ months × 12)</t>
+          <t>run_rate</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[0].yearEnd</t>
-        </is>
-      </c>
-      <c r="B244" s="5" t="n">
-        <v>46504248.46</v>
+          <t>projections.methods[0].label</t>
+        </is>
+      </c>
+      <c r="B244" s="13" t="inlineStr">
+        <is>
+          <t>Run-rate (YTD ÷ months × 12)</t>
+        </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[0].assumption</t>
-        </is>
-      </c>
-      <c r="B245" s="13" t="inlineStr">
-        <is>
-          <t>YTD avg monthly $3,875,354 continues for 7 months</t>
-        </is>
+          <t>projections.methods[0].yearEnd</t>
+        </is>
+      </c>
+      <c r="B245" s="5" t="n">
+        <v>60265981.14</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[0].confidence</t>
+          <t>projections.methods[0].assumption</t>
         </is>
       </c>
       <c r="B246" s="13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>YTD avg monthly $5,022,165 continues for 6 months</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[1].id</t>
+          <t>projections.methods[0].confidence</t>
         </is>
       </c>
       <c r="B247" s="13" t="inlineStr">
         <is>
-          <t>yoy_adjusted</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[1].label</t>
+          <t>projections.methods[1].id</t>
         </is>
       </c>
       <c r="B248" s="13" t="inlineStr">
         <is>
-          <t>YoY growth-adjusted</t>
+          <t>yoy_adjusted</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[1].yearEnd</t>
-        </is>
-      </c>
-      <c r="B249" s="5" t="n">
-        <v>47158830.4</v>
+          <t>projections.methods[1].label</t>
+        </is>
+      </c>
+      <c r="B249" s="13" t="inlineStr">
+        <is>
+          <t>YoY growth-adjusted</t>
+        </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[1].assumption</t>
-        </is>
-      </c>
-      <c r="B250" s="13" t="inlineStr">
-        <is>
-          <t>Apply prior-year YoY growth +2.4% to remaining 7 months</t>
-        </is>
+          <t>projections.methods[1].yearEnd</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="n">
+        <v>60993085.63</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[1].yoyGrowth</t>
-        </is>
-      </c>
-      <c r="B251" s="6" t="n">
-        <v>0.02412984854137568</v>
+          <t>projections.methods[1].assumption</t>
+        </is>
+      </c>
+      <c r="B251" s="13" t="inlineStr">
+        <is>
+          <t>Apply prior-year YoY growth +2.4% to remaining 6 months</t>
+        </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[1].confidence</t>
-        </is>
-      </c>
-      <c r="B252" s="13" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
+          <t>projections.methods[1].yoyGrowth</t>
+        </is>
+      </c>
+      <c r="B252" s="6" t="n">
+        <v>0.02412984828845288</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[2].id</t>
+          <t>projections.methods[1].confidence</t>
         </is>
       </c>
       <c r="B253" s="13" t="inlineStr">
         <is>
-          <t>seasonality_adjusted</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[2].label</t>
+          <t>projections.methods[2].id</t>
         </is>
       </c>
       <c r="B254" s="13" t="inlineStr">
         <is>
-          <t>Seasonality-adjusted (prior-year monthly avg)</t>
+          <t>seasonality_adjusted</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[2].yearEnd</t>
-        </is>
-      </c>
-      <c r="B255" s="5" t="n">
-        <v>42996995.85</v>
+          <t>projections.methods[2].label</t>
+        </is>
+      </c>
+      <c r="B255" s="13" t="inlineStr">
+        <is>
+          <t>Seasonality-adjusted (prior-year monthly avg)</t>
+        </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[2].assumption</t>
-        </is>
-      </c>
-      <c r="B256" s="13" t="inlineStr">
-        <is>
-          <t>YTD actual + prior-year avg monthly $3,374,318 × 7 remaining months</t>
-        </is>
+          <t>projections.methods[2].yearEnd</t>
+        </is>
+      </c>
+      <c r="B256" s="5" t="n">
+        <v>50378898.27</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[2].confidence</t>
+          <t>projections.methods[2].assumption</t>
         </is>
       </c>
       <c r="B257" s="13" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>YTD actual + prior-year avg monthly $3,374,318 × 6 remaining months</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[3].id</t>
+          <t>projections.methods[2].confidence</t>
         </is>
       </c>
       <c r="B258" s="13" t="inlineStr">
         <is>
-          <t>pipeline_driven</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[3].label</t>
+          <t>projections.methods[3].id</t>
         </is>
       </c>
       <c r="B259" s="13" t="inlineStr">
         <is>
-          <t>Pipeline-driven (open invoices billing cadence)</t>
+          <t>pipeline_driven</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[3].yearEnd</t>
-        </is>
-      </c>
-      <c r="B260" s="5" t="n">
-        <v>52919774.6</v>
+          <t>projections.methods[3].label</t>
+        </is>
+      </c>
+      <c r="B260" s="13" t="inlineStr">
+        <is>
+          <t>Pipeline-driven (open invoices billing cadence)</t>
+        </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[3].yearEndBillings</t>
+          <t>projections.methods[3].yearEnd</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
-        <v>44902063.06</v>
+        <v>66292579.25</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[3].assumption</t>
-        </is>
-      </c>
-      <c r="B262" s="13" t="inlineStr">
-        <is>
-          <t>Avg billings $4,065,858/mo × 7 remaining + YTD; recognized at YTD billings→revenue ratio of 1.18</t>
-        </is>
+          <t>projections.methods[3].yearEndBillings</t>
+        </is>
+      </c>
+      <c r="B262" s="5" t="n">
+        <v>46494737.43</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[3].billingsToRevenueRatio</t>
-        </is>
-      </c>
-      <c r="B263" s="5" t="n">
-        <v>1.178559981161696</v>
+          <t>projections.methods[3].assumption</t>
+        </is>
+      </c>
+      <c r="B263" s="13" t="inlineStr">
+        <is>
+          <t>Avg billings $4,226,794/mo × 6 remaining + YTD; recognized at YTD billings→revenue ratio of 1.43</t>
+        </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[3].ytdBillings</t>
+          <t>projections.methods[3].billingsToRevenueRatio</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
-        <v>16441055.61</v>
+        <v>1.425808229392734</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[3].avgMonthlyBillings</t>
+          <t>projections.methods[3].ytdBillings</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
-        <v>4065858.21</v>
+        <v>21133971.56</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="29" t="inlineStr">
         <is>
-          <t>projections.methods[3].confidence</t>
-        </is>
-      </c>
-      <c r="B266" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
+          <t>projections.methods[3].avgMonthlyBillings</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="n">
+        <v>4226794.31</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="29" t="inlineStr">
         <is>
-          <t>projections.consensus</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="n">
-        <v>47394962.33</v>
+          <t>projections.methods[3].confidence</t>
+        </is>
+      </c>
+      <c r="B267" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="29" t="inlineStr">
         <is>
-          <t>projections.low</t>
+          <t>projections.consensus</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
-        <v>42996995.85</v>
+        <v>59482636.07</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="29" t="inlineStr">
         <is>
-          <t>projections.high</t>
+          <t>projections.low</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
-        <v>52919774.6</v>
+        <v>50378898.27</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="29" t="inlineStr">
         <is>
-          <t>projections.spread</t>
+          <t>projections.high</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
-        <v>9922778.75</v>
+        <v>66292579.25</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="29" t="inlineStr">
         <is>
-          <t>multiYear.anchor.year</t>
+          <t>projections.spread</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
-        <v>2026</v>
+        <v>15913680.98</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="29" t="inlineStr">
         <is>
-          <t>multiYear.anchor.revenue</t>
+          <t>multiYear.anchor.year</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
-        <v>46504248.46</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="29" t="inlineStr">
         <is>
-          <t>multiYear.anchor.grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B273" s="6" t="n">
-        <v>0.2718606081952797</v>
+          <t>multiYear.anchor.revenue</t>
+        </is>
+      </c>
+      <c r="B273" s="5" t="n">
+        <v>60265981.14</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="29" t="inlineStr">
         <is>
-          <t>multiYear.anchor.netMarginPct</t>
+          <t>multiYear.anchor.grossMarginPct</t>
         </is>
       </c>
       <c r="B274" s="6" t="n">
-        <v>0.08575153307616747</v>
+        <v>0.3332844835520087</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="29" t="inlineStr">
         <is>
-          <t>multiYear.baseCagr</t>
+          <t>multiYear.anchor.netMarginPct</t>
         </is>
       </c>
       <c r="B275" s="6" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.15931660911146</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.label</t>
-        </is>
-      </c>
-      <c r="B276" s="13" t="inlineStr">
-        <is>
-          <t>Bearish</t>
-        </is>
+          <t>multiYear.baseCagr</t>
+        </is>
+      </c>
+      <c r="B276" s="6" t="n">
+        <v>0.2346</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.growth</t>
-        </is>
-      </c>
-      <c r="B277" s="6" t="n">
-        <v>0.0345</v>
+          <t>multiYear.scenarios.bearish.label</t>
+        </is>
+      </c>
+      <c r="B277" s="13" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.gmShift</t>
+          <t>multiYear.scenarios.bearish.growth</t>
         </is>
       </c>
       <c r="B278" s="6" t="n">
-        <v>-0.02</v>
+        <v>0.1846</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[0].year</t>
-        </is>
-      </c>
-      <c r="B279" s="5" t="n">
-        <v>2027</v>
+          <t>multiYear.scenarios.bearish.gmShift</t>
+        </is>
+      </c>
+      <c r="B279" s="6" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[0].revenue</t>
+          <t>multiYear.scenarios.bearish.years[0].year</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
-        <v>48109881.41</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[0].grossProfit</t>
+          <t>multiYear.scenarios.bearish.years[0].revenue</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
-        <v>12116983.99</v>
+        <v>71391720.43000001</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[0].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B282" s="6" t="n">
-        <v>0.2518606081952797</v>
+          <t>multiYear.scenarios.bearish.years[0].grossProfit</t>
+        </is>
+      </c>
+      <c r="B282" s="5" t="n">
+        <v>22365918.26</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[0].netIncome</t>
-        </is>
-      </c>
-      <c r="B283" s="5" t="n">
-        <v>3451957.75</v>
+          <t>multiYear.scenarios.bearish.years[0].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B283" s="6" t="n">
+        <v>0.3132844835520087</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[0].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B284" s="6" t="n">
-        <v>0.07175153307616747</v>
+          <t>multiYear.scenarios.bearish.years[0].netIncome</t>
+        </is>
+      </c>
+      <c r="B284" s="5" t="n">
+        <v>10374402.73</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[1].year</t>
-        </is>
-      </c>
-      <c r="B285" s="5" t="n">
-        <v>2028</v>
+          <t>multiYear.scenarios.bearish.years[0].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B285" s="6" t="n">
+        <v>0.14531660911146</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[1].revenue</t>
+          <t>multiYear.scenarios.bearish.years[1].year</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
-        <v>49770951.38</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[1].grossProfit</t>
+          <t>multiYear.scenarios.bearish.years[1].revenue</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
-        <v>11539923.06</v>
+        <v>84571389.19</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[1].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B288" s="6" t="n">
-        <v>0.2318606081952797</v>
+          <t>multiYear.scenarios.bearish.years[1].grossProfit</t>
+        </is>
+      </c>
+      <c r="B288" s="5" t="n">
+        <v>24803476.2</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[1].netIncome</t>
-        </is>
-      </c>
-      <c r="B289" s="5" t="n">
-        <v>2874348.75</v>
+          <t>multiYear.scenarios.bearish.years[1].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="n">
+        <v>0.2932844835520087</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.bearish.years[1].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="n">
-        <v>0.05775153307616747</v>
+          <t>multiYear.scenarios.bearish.years[1].netIncome</t>
+        </is>
+      </c>
+      <c r="B290" s="5" t="n">
+        <v>11105628.06</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.label</t>
-        </is>
-      </c>
-      <c r="B291" s="13" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
+          <t>multiYear.scenarios.bearish.years[1].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B291" s="6" t="n">
+        <v>0.13131660911146</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.growth</t>
-        </is>
-      </c>
-      <c r="B292" s="6" t="n">
-        <v>0.08450000000000001</v>
+          <t>multiYear.scenarios.base.label</t>
+        </is>
+      </c>
+      <c r="B292" s="13" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.gmShift</t>
+          <t>multiYear.scenarios.base.growth</t>
         </is>
       </c>
       <c r="B293" s="6" t="n">
-        <v>0</v>
+        <v>0.2346</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[0].year</t>
-        </is>
-      </c>
-      <c r="B294" s="5" t="n">
-        <v>2027</v>
+          <t>multiYear.scenarios.base.gmShift</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[0].revenue</t>
+          <t>multiYear.scenarios.base.years[0].year</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
-        <v>50435093.83</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[0].grossProfit</t>
+          <t>multiYear.scenarios.base.years[0].revenue</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
-        <v>13711315.28</v>
+        <v>74405019.48</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[0].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B297" s="6" t="n">
-        <v>0.2718606081952797</v>
+          <t>multiYear.scenarios.base.years[0].grossProfit</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="n">
+        <v>24798038.49</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[0].netIncome</t>
-        </is>
-      </c>
-      <c r="B298" s="5" t="n">
-        <v>4324886.62</v>
+          <t>multiYear.scenarios.base.years[0].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="n">
+        <v>0.3332844835520087</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[0].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B299" s="6" t="n">
-        <v>0.08575153307616747</v>
+          <t>multiYear.scenarios.base.years[0].netIncome</t>
+        </is>
+      </c>
+      <c r="B299" s="5" t="n">
+        <v>11853955.41</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[1].year</t>
-        </is>
-      </c>
-      <c r="B300" s="5" t="n">
-        <v>2028</v>
+          <t>multiYear.scenarios.base.years[0].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B300" s="6" t="n">
+        <v>0.15931660911146</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[1].revenue</t>
+          <t>multiYear.scenarios.base.years[1].year</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
-        <v>54698200.15</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[1].grossProfit</t>
+          <t>multiYear.scenarios.base.years[1].revenue</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
-        <v>14870285.96</v>
+        <v>91861226.18000001</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[1].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B303" s="6" t="n">
-        <v>0.2718606081952797</v>
+          <t>multiYear.scenarios.base.years[1].grossProfit</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="n">
+        <v>30615921.33</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[1].netIncome</t>
-        </is>
-      </c>
-      <c r="B304" s="5" t="n">
-        <v>4690454.52</v>
+          <t>multiYear.scenarios.base.years[1].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B304" s="6" t="n">
+        <v>0.3332844835520087</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.base.years[1].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B305" s="6" t="n">
-        <v>0.08575153307616747</v>
+          <t>multiYear.scenarios.base.years[1].netIncome</t>
+        </is>
+      </c>
+      <c r="B305" s="5" t="n">
+        <v>14635019.06</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.label</t>
-        </is>
-      </c>
-      <c r="B306" s="13" t="inlineStr">
-        <is>
-          <t>Optimistic</t>
-        </is>
+          <t>multiYear.scenarios.base.years[1].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B306" s="6" t="n">
+        <v>0.15931660911146</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.growth</t>
-        </is>
-      </c>
-      <c r="B307" s="6" t="n">
-        <v>0.1245</v>
+          <t>multiYear.scenarios.optimistic.label</t>
+        </is>
+      </c>
+      <c r="B307" s="13" t="inlineStr">
+        <is>
+          <t>Optimistic</t>
+        </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.gmShift</t>
+          <t>multiYear.scenarios.optimistic.growth</t>
         </is>
       </c>
       <c r="B308" s="6" t="n">
-        <v>0.015</v>
+        <v>0.2746</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[0].year</t>
-        </is>
-      </c>
-      <c r="B309" s="5" t="n">
-        <v>2027</v>
+          <t>multiYear.scenarios.optimistic.gmShift</t>
+        </is>
+      </c>
+      <c r="B309" s="6" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[0].revenue</t>
+          <t>multiYear.scenarios.optimistic.years[0].year</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
-        <v>52295263.77</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[0].grossProfit</t>
+          <t>multiYear.scenarios.optimistic.years[0].revenue</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
-        <v>15001451.17</v>
+        <v>76815658.73</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[0].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B312" s="6" t="n">
-        <v>0.2868606081952797</v>
+          <t>multiYear.scenarios.optimistic.years[0].grossProfit</t>
+        </is>
+      </c>
+      <c r="B312" s="5" t="n">
+        <v>26753702.03</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[0].netIncome</t>
-        </is>
-      </c>
-      <c r="B313" s="5" t="n">
-        <v>5033499.31</v>
+          <t>multiYear.scenarios.optimistic.years[0].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B313" s="6" t="n">
+        <v>0.3482844835520088</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[0].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B314" s="6" t="n">
-        <v>0.09625153307616746</v>
+          <t>multiYear.scenarios.optimistic.years[0].netIncome</t>
+        </is>
+      </c>
+      <c r="B314" s="5" t="n">
+        <v>13044574.69</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[1].year</t>
-        </is>
-      </c>
-      <c r="B315" s="5" t="n">
-        <v>2028</v>
+          <t>multiYear.scenarios.optimistic.years[0].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B315" s="6" t="n">
+        <v>0.16981660911146</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[1].revenue</t>
+          <t>multiYear.scenarios.optimistic.years[1].year</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
-        <v>58807414.45</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[1].grossProfit</t>
+          <t>multiYear.scenarios.optimistic.years[1].revenue</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
-        <v>17751641.89</v>
+        <v>97910053.31</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[1].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B318" s="6" t="n">
-        <v>0.3018606081952797</v>
+          <t>multiYear.scenarios.optimistic.years[1].grossProfit</t>
+        </is>
+      </c>
+      <c r="B318" s="5" t="n">
+        <v>35569203.15</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[1].netIncome</t>
-        </is>
-      </c>
-      <c r="B319" s="5" t="n">
-        <v>6277781.65</v>
+          <t>multiYear.scenarios.optimistic.years[1].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B319" s="6" t="n">
+        <v>0.3632844835520088</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="29" t="inlineStr">
         <is>
-          <t>multiYear.scenarios.optimistic.years[1].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B320" s="6" t="n">
-        <v>0.1067515330761675</v>
+          <t>multiYear.scenarios.optimistic.years[1].netIncome</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="n">
+        <v>17654808.81</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="29" t="inlineStr">
         <is>
-          <t>pipeline.asOf</t>
-        </is>
-      </c>
-      <c r="B321" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
+          <t>multiYear.scenarios.optimistic.years[1].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B321" s="6" t="n">
+        <v>0.18031660911146</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="29" t="inlineStr">
         <is>
-          <t>pipeline.periodStart</t>
+          <t>pipeline.asOf</t>
         </is>
       </c>
       <c r="B322" s="13" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="29" t="inlineStr">
         <is>
-          <t>pipeline.periodEnd</t>
+          <t>pipeline.periodStart</t>
         </is>
       </c>
       <c r="B323" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-01-01</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="29" t="inlineStr">
         <is>
-          <t>pipeline.invoiceCount</t>
-        </is>
-      </c>
-      <c r="B324" s="5" t="n">
-        <v>406</v>
+          <t>pipeline.periodEnd</t>
+        </is>
+      </c>
+      <c r="B324" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="29" t="inlineStr">
         <is>
-          <t>pipeline.ytdBillings</t>
+          <t>pipeline.invoiceCount</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
-        <v>16441055.61</v>
+        <v>500</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="29" t="inlineStr">
         <is>
-          <t>pipeline.ytdOpenBalance</t>
+          <t>pipeline.ytdBillings</t>
         </is>
       </c>
       <c r="B326" s="5" t="n">
-        <v>3518300.82</v>
+        <v>21133971.56</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="29" t="inlineStr">
         <is>
-          <t>pipeline.ytdCollected</t>
+          <t>pipeline.ytdOpenBalance</t>
         </is>
       </c>
       <c r="B327" s="5" t="n">
-        <v>12922754.79</v>
+        <v>9713221.890000001</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="29" t="inlineStr">
         <is>
-          <t>pipeline.openInvoiceCount</t>
+          <t>pipeline.ytdCollected</t>
         </is>
       </c>
       <c r="B328" s="5" t="n">
-        <v>66</v>
+        <v>11420749.67</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[0].month</t>
-        </is>
-      </c>
-      <c r="B329" s="13" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
+          <t>pipeline.openInvoiceCount</t>
+        </is>
+      </c>
+      <c r="B329" s="5" t="n">
+        <v>197</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[0].billings</t>
-        </is>
-      </c>
-      <c r="B330" s="5" t="n">
-        <v>2732933.77</v>
+          <t>pipeline.monthlyBillings[0].month</t>
+        </is>
+      </c>
+      <c r="B330" s="13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[0].openBalance</t>
+          <t>pipeline.monthlyBillings[0].billings</t>
         </is>
       </c>
       <c r="B331" s="5" t="n">
-        <v>82181.03999999999</v>
+        <v>1121181.05</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[0].count</t>
+          <t>pipeline.monthlyBillings[0].openBalance</t>
         </is>
       </c>
       <c r="B332" s="5" t="n">
-        <v>90</v>
+        <v>98794.71000000001</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[1].month</t>
-        </is>
-      </c>
-      <c r="B333" s="13" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
+          <t>pipeline.monthlyBillings[0].count</t>
+        </is>
+      </c>
+      <c r="B333" s="5" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[1].billings</t>
-        </is>
-      </c>
-      <c r="B334" s="5" t="n">
-        <v>3783851.42</v>
+          <t>pipeline.monthlyBillings[1].month</t>
+        </is>
+      </c>
+      <c r="B334" s="13" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[1].openBalance</t>
+          <t>pipeline.monthlyBillings[1].billings</t>
         </is>
       </c>
       <c r="B335" s="5" t="n">
-        <v>243933.33</v>
+        <v>4814613.14</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[1].count</t>
+          <t>pipeline.monthlyBillings[1].openBalance</t>
         </is>
       </c>
       <c r="B336" s="5" t="n">
-        <v>91</v>
+        <v>418077.52</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[2].month</t>
-        </is>
-      </c>
-      <c r="B337" s="13" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
+          <t>pipeline.monthlyBillings[1].count</t>
+        </is>
+      </c>
+      <c r="B337" s="5" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[2].billings</t>
-        </is>
-      </c>
-      <c r="B338" s="5" t="n">
-        <v>4814613.14</v>
+          <t>pipeline.monthlyBillings[2].month</t>
+        </is>
+      </c>
+      <c r="B338" s="13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[2].openBalance</t>
+          <t>pipeline.monthlyBillings[2].billings</t>
         </is>
       </c>
       <c r="B339" s="5" t="n">
-        <v>693136.46</v>
+        <v>4932094.5</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[2].count</t>
+          <t>pipeline.monthlyBillings[2].openBalance</t>
         </is>
       </c>
       <c r="B340" s="5" t="n">
-        <v>99</v>
+        <v>801999.36</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[3].month</t>
-        </is>
-      </c>
-      <c r="B341" s="13" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
+          <t>pipeline.monthlyBillings[2].count</t>
+        </is>
+      </c>
+      <c r="B341" s="5" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[3].billings</t>
-        </is>
-      </c>
-      <c r="B342" s="5" t="n">
-        <v>4932034.5</v>
+          <t>pipeline.monthlyBillings[3].month</t>
+        </is>
+      </c>
+      <c r="B342" s="13" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[3].openBalance</t>
+          <t>pipeline.monthlyBillings[3].billings</t>
         </is>
       </c>
       <c r="B343" s="5" t="n">
-        <v>2397076.37</v>
+        <v>5304957.23</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[3].count</t>
+          <t>pipeline.monthlyBillings[3].openBalance</t>
         </is>
       </c>
       <c r="B344" s="5" t="n">
-        <v>104</v>
+        <v>3572169.6</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[4].month</t>
-        </is>
-      </c>
-      <c r="B345" s="13" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
+          <t>pipeline.monthlyBillings[3].count</t>
+        </is>
+      </c>
+      <c r="B345" s="5" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[4].billings</t>
-        </is>
-      </c>
-      <c r="B346" s="5" t="n">
-        <v>177622.78</v>
+          <t>pipeline.monthlyBillings[4].month</t>
+        </is>
+      </c>
+      <c r="B346" s="13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[4].openBalance</t>
+          <t>pipeline.monthlyBillings[4].billings</t>
         </is>
       </c>
       <c r="B347" s="5" t="n">
-        <v>101973.62</v>
+        <v>4961125.64</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="29" t="inlineStr">
         <is>
-          <t>pipeline.monthlyBillings[4].count</t>
+          <t>pipeline.monthlyBillings[4].openBalance</t>
         </is>
       </c>
       <c r="B348" s="5" t="n">
-        <v>22</v>
+        <v>4822180.7</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="29" t="inlineStr">
         <is>
-          <t>customers.period</t>
-        </is>
-      </c>
-      <c r="B349" s="13" t="inlineStr">
-        <is>
-          <t>THIS_YEAR_TO_DATE_2026</t>
-        </is>
+          <t>pipeline.monthlyBillings[4].count</t>
+        </is>
+      </c>
+      <c r="B349" s="5" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="29" t="inlineStr">
         <is>
-          <t>customers.totalSales</t>
-        </is>
-      </c>
-      <c r="B350" s="5" t="n">
-        <v>75418579.22000004</v>
+          <t>customers.period</t>
+        </is>
+      </c>
+      <c r="B350" s="13" t="inlineStr">
+        <is>
+          <t>THIS_YEAR_TO_DATE_2026</t>
+        </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="29" t="inlineStr">
         <is>
-          <t>customers.customerCount</t>
+          <t>customers.totalSales</t>
         </is>
       </c>
       <c r="B351" s="5" t="n">
-        <v>282</v>
+        <v>77174311.24000002</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="29" t="inlineStr">
         <is>
-          <t>customers.top5Concentration</t>
+          <t>customers.customerCount</t>
         </is>
       </c>
       <c r="B352" s="5" t="n">
-        <v>17.7</v>
+        <v>295</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[0].name</t>
-        </is>
-      </c>
-      <c r="B353" s="13" t="inlineStr">
-        <is>
-          <t>Thompson Thrift Construction</t>
-        </is>
+          <t>customers.top5Concentration</t>
+        </is>
+      </c>
+      <c r="B353" s="5" t="n">
+        <v>17.3</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[0].sales</t>
-        </is>
-      </c>
-      <c r="B354" s="5" t="n">
-        <v>2717218.65</v>
+          <t>customers.topCustomers[0].name</t>
+        </is>
+      </c>
+      <c r="B354" s="13" t="inlineStr">
+        <is>
+          <t>Thompson Thrift Construction</t>
+        </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[0].percent</t>
+          <t>customers.topCustomers[0].sales</t>
         </is>
       </c>
       <c r="B355" s="5" t="n">
-        <v>3.6</v>
+        <v>2717218.65</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[1].name</t>
-        </is>
-      </c>
-      <c r="B356" s="13" t="inlineStr">
-        <is>
-          <t>MF.2025.972 Union Flats - Fishers</t>
-        </is>
+          <t>customers.topCustomers[0].percent</t>
+        </is>
+      </c>
+      <c r="B356" s="5" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[1].sales</t>
-        </is>
-      </c>
-      <c r="B357" s="5" t="n">
-        <v>2717218.65</v>
+          <t>customers.topCustomers[1].name</t>
+        </is>
+      </c>
+      <c r="B357" s="13" t="inlineStr">
+        <is>
+          <t>MF.2025.972 Union Flats - Fishers</t>
+        </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[1].percent</t>
+          <t>customers.topCustomers[1].sales</t>
         </is>
       </c>
       <c r="B358" s="5" t="n">
-        <v>3.6</v>
+        <v>2717218.65</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[2].name</t>
-        </is>
-      </c>
-      <c r="B359" s="13" t="inlineStr">
-        <is>
-          <t>The Peterson Company, LLC</t>
-        </is>
+          <t>customers.topCustomers[1].percent</t>
+        </is>
+      </c>
+      <c r="B359" s="5" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[2].sales</t>
-        </is>
-      </c>
-      <c r="B360" s="5" t="n">
-        <v>2587643.01</v>
+          <t>customers.topCustomers[2].name</t>
+        </is>
+      </c>
+      <c r="B360" s="13" t="inlineStr">
+        <is>
+          <t>The Peterson Company, LLC</t>
+        </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[2].percent</t>
+          <t>customers.topCustomers[2].sales</t>
         </is>
       </c>
       <c r="B361" s="5" t="n">
-        <v>3.4</v>
+        <v>2587643.01</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[3].name</t>
-        </is>
-      </c>
-      <c r="B362" s="13" t="inlineStr">
-        <is>
-          <t>DEEM, LLC</t>
-        </is>
+          <t>customers.topCustomers[2].percent</t>
+        </is>
+      </c>
+      <c r="B362" s="5" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[3].sales</t>
-        </is>
-      </c>
-      <c r="B363" s="5" t="n">
-        <v>2041679.82</v>
+          <t>customers.topCustomers[3].name</t>
+        </is>
+      </c>
+      <c r="B363" s="13" t="inlineStr">
+        <is>
+          <t>DEEM, LLC</t>
+        </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[3].percent</t>
+          <t>customers.topCustomers[3].sales</t>
         </is>
       </c>
       <c r="B364" s="5" t="n">
-        <v>2.7</v>
+        <v>2065681.07</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[4].name</t>
-        </is>
-      </c>
-      <c r="B365" s="13" t="inlineStr">
-        <is>
-          <t>Marous Brothers Construction</t>
-        </is>
+          <t>customers.topCustomers[3].percent</t>
+        </is>
+      </c>
+      <c r="B365" s="5" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[4].sales</t>
-        </is>
-      </c>
-      <c r="B366" s="5" t="n">
-        <v>2039464.17</v>
+          <t>customers.topCustomers[4].name</t>
+        </is>
+      </c>
+      <c r="B366" s="13" t="inlineStr">
+        <is>
+          <t>Marous Brothers Construction</t>
+        </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[4].percent</t>
+          <t>customers.topCustomers[4].sales</t>
         </is>
       </c>
       <c r="B367" s="5" t="n">
-        <v>2.7</v>
+        <v>2039464.17</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[5].name</t>
-        </is>
-      </c>
-      <c r="B368" s="13" t="inlineStr">
-        <is>
-          <t>MF.2025.1019 Town &amp; Country Apartments (NY MF Project - 22 bldgs)</t>
-        </is>
+          <t>customers.topCustomers[4].percent</t>
+        </is>
+      </c>
+      <c r="B368" s="5" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[5].sales</t>
-        </is>
-      </c>
-      <c r="B369" s="5" t="n">
-        <v>2039464.17</v>
+          <t>customers.topCustomers[5].name</t>
+        </is>
+      </c>
+      <c r="B369" s="13" t="inlineStr">
+        <is>
+          <t>MF.2025.1019 Town &amp; Country Apartments (NY MF Project - 22 bldgs)</t>
+        </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[5].percent</t>
+          <t>customers.topCustomers[5].sales</t>
         </is>
       </c>
       <c r="B370" s="5" t="n">
-        <v>2.7</v>
+        <v>2039464.17</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[6].name</t>
-        </is>
-      </c>
-      <c r="B371" s="13" t="inlineStr">
-        <is>
-          <t>Skender Construction of Indiana LLC</t>
-        </is>
+          <t>customers.topCustomers[5].percent</t>
+        </is>
+      </c>
+      <c r="B371" s="5" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[6].sales</t>
-        </is>
-      </c>
-      <c r="B372" s="5" t="n">
-        <v>2035601.3</v>
+          <t>customers.topCustomers[6].name</t>
+        </is>
+      </c>
+      <c r="B372" s="13" t="inlineStr">
+        <is>
+          <t>Skender Construction of Indiana LLC</t>
+        </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[6].percent</t>
+          <t>customers.topCustomers[6].sales</t>
         </is>
       </c>
       <c r="B373" s="5" t="n">
-        <v>2.7</v>
+        <v>1974491.3</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[7].name</t>
-        </is>
-      </c>
-      <c r="B374" s="13" t="inlineStr">
-        <is>
-          <t>MILHAUS Construction</t>
-        </is>
+          <t>customers.topCustomers[6].percent</t>
+        </is>
+      </c>
+      <c r="B374" s="5" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[7].sales</t>
-        </is>
-      </c>
-      <c r="B375" s="5" t="n">
-        <v>1886647.5</v>
+          <t>customers.topCustomers[7].name</t>
+        </is>
+      </c>
+      <c r="B375" s="13" t="inlineStr">
+        <is>
+          <t>MILHAUS Construction</t>
+        </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[7].percent</t>
+          <t>customers.topCustomers[7].sales</t>
         </is>
       </c>
       <c r="B376" s="5" t="n">
-        <v>2.5</v>
+        <v>1886647.5</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[8].name</t>
-        </is>
-      </c>
-      <c r="B377" s="13" t="inlineStr">
-        <is>
-          <t>Compass Commercial Construction Group</t>
-        </is>
+          <t>customers.topCustomers[7].percent</t>
+        </is>
+      </c>
+      <c r="B377" s="5" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[8].sales</t>
-        </is>
-      </c>
-      <c r="B378" s="5" t="n">
-        <v>1704370.92</v>
+          <t>customers.topCustomers[8].name</t>
+        </is>
+      </c>
+      <c r="B378" s="13" t="inlineStr">
+        <is>
+          <t>Compass Commercial Construction Group</t>
+        </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[8].percent</t>
+          <t>customers.topCustomers[8].sales</t>
         </is>
       </c>
       <c r="B379" s="5" t="n">
-        <v>2.3</v>
+        <v>1852274.33</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[9].name</t>
-        </is>
-      </c>
-      <c r="B380" s="13" t="inlineStr">
-        <is>
-          <t>2025.964 Avon Municipal Building</t>
-        </is>
+          <t>customers.topCustomers[8].percent</t>
+        </is>
+      </c>
+      <c r="B380" s="5" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[9].sales</t>
-        </is>
-      </c>
-      <c r="B381" s="5" t="n">
-        <v>1361655.46</v>
+          <t>verifiedMonths[0].periodStart</t>
+        </is>
+      </c>
+      <c r="B381" s="13" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="29" t="inlineStr">
         <is>
-          <t>customers.topCustomers[9].percent</t>
-        </is>
-      </c>
-      <c r="B382" s="5" t="n">
-        <v>1.8</v>
+          <t>verifiedMonths[0].periodEnd</t>
+        </is>
+      </c>
+      <c r="B382" s="13" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].periodStart</t>
-        </is>
-      </c>
-      <c r="B383" s="13" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
+          <t>verifiedMonths[0].revenue</t>
+        </is>
+      </c>
+      <c r="B383" s="5" t="n">
+        <v>2041295.53</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].periodEnd</t>
-        </is>
-      </c>
-      <c r="B384" s="13" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
+          <t>verifiedMonths[0].cogs</t>
+        </is>
+      </c>
+      <c r="B384" s="5" t="n">
+        <v>1705779.19</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].revenue</t>
+          <t>verifiedMonths[0].grossProfit</t>
         </is>
       </c>
       <c r="B385" s="5" t="n">
-        <v>2041295.53</v>
+        <v>335516.34</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].cogs</t>
+          <t>verifiedMonths[0].operatingExpenses</t>
         </is>
       </c>
       <c r="B386" s="5" t="n">
-        <v>1705779.19</v>
+        <v>917633.4300000001</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].grossProfit</t>
+          <t>verifiedMonths[0].netIncome</t>
         </is>
       </c>
       <c r="B387" s="5" t="n">
-        <v>335516.34</v>
+        <v>-582117</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B388" s="5" t="n">
-        <v>917633.4300000001</v>
+          <t>verifiedMonths[0].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B388" s="6" t="n">
+        <v>0.1643644122416709</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].netIncome</t>
-        </is>
-      </c>
-      <c r="B389" s="5" t="n">
-        <v>-582117</v>
+          <t>verifiedMonths[0].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B389" s="6" t="n">
+        <v>-0.285170369231152</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B390" s="6" t="n">
-        <v>0.1643644122416709</v>
+          <t>verifiedMonths[0].month</t>
+        </is>
+      </c>
+      <c r="B390" s="13" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B391" s="6" t="n">
-        <v>-0.285170369231152</v>
+          <t>verifiedMonths[1].periodStart</t>
+        </is>
+      </c>
+      <c r="B391" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[0].month</t>
+          <t>verifiedMonths[1].periodEnd</t>
         </is>
       </c>
       <c r="B392" s="13" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-04-30</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].periodStart</t>
-        </is>
-      </c>
-      <c r="B393" s="13" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
+          <t>verifiedMonths[1].revenue</t>
+        </is>
+      </c>
+      <c r="B393" s="5" t="n">
+        <v>2424157.48</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].periodEnd</t>
-        </is>
-      </c>
-      <c r="B394" s="13" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
-        </is>
+          <t>verifiedMonths[1].cogs</t>
+        </is>
+      </c>
+      <c r="B394" s="5" t="n">
+        <v>1668995.34</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].revenue</t>
+          <t>verifiedMonths[1].grossProfit</t>
         </is>
       </c>
       <c r="B395" s="5" t="n">
-        <v>2424157.48</v>
+        <v>755162.14</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].cogs</t>
+          <t>verifiedMonths[1].operatingExpenses</t>
         </is>
       </c>
       <c r="B396" s="5" t="n">
-        <v>1668995.34</v>
+        <v>836162.72</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].grossProfit</t>
+          <t>verifiedMonths[1].netIncome</t>
         </is>
       </c>
       <c r="B397" s="5" t="n">
-        <v>755162.14</v>
+        <v>-69968.27</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B398" s="5" t="n">
-        <v>836162.72</v>
+          <t>verifiedMonths[1].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B398" s="6" t="n">
+        <v>0.3115152980902874</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].netIncome</t>
-        </is>
-      </c>
-      <c r="B399" s="5" t="n">
-        <v>-69968.27</v>
+          <t>verifiedMonths[1].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B399" s="6" t="n">
+        <v>-0.02886292271738056</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B400" s="6" t="n">
-        <v>0.3115152980902874</v>
+          <t>verifiedMonths[1].month</t>
+        </is>
+      </c>
+      <c r="B400" s="13" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B401" s="6" t="n">
-        <v>-0.02886292271738056</v>
+          <t>verifiedMonths[2].periodStart</t>
+        </is>
+      </c>
+      <c r="B401" s="13" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[1].month</t>
+          <t>verifiedMonths[2].periodEnd</t>
         </is>
       </c>
       <c r="B402" s="13" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].periodStart</t>
-        </is>
-      </c>
-      <c r="B403" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+          <t>verifiedMonths[2].revenue</t>
+        </is>
+      </c>
+      <c r="B403" s="5" t="n">
+        <v>3347154.03</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].periodEnd</t>
-        </is>
-      </c>
-      <c r="B404" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
+          <t>verifiedMonths[2].cogs</t>
+        </is>
+      </c>
+      <c r="B404" s="5" t="n">
+        <v>1995316.63</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].revenue</t>
+          <t>verifiedMonths[2].grossProfit</t>
         </is>
       </c>
       <c r="B405" s="5" t="n">
-        <v>5290349.77</v>
+        <v>1351837.4</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].cogs</t>
+          <t>verifiedMonths[2].operatingExpenses</t>
         </is>
       </c>
       <c r="B406" s="5" t="n">
-        <v>3616852.68</v>
+        <v>879964.46</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].grossProfit</t>
+          <t>verifiedMonths[2].netIncome</t>
         </is>
       </c>
       <c r="B407" s="5" t="n">
-        <v>1673497.09</v>
+        <v>597004.63</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B408" s="5" t="n">
-        <v>897079.72</v>
+          <t>verifiedMonths[2].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B408" s="6" t="n">
+        <v>0.4038766629452065</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].netIncome</t>
-        </is>
-      </c>
-      <c r="B409" s="5" t="n">
-        <v>790908.5600000001</v>
+          <t>verifiedMonths[2].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B409" s="6" t="n">
+        <v>0.1783618634365624</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B410" s="6" t="n">
-        <v>0.3163301412488649</v>
+          <t>verifiedMonths[2].month</t>
+        </is>
+      </c>
+      <c r="B410" s="13" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B411" s="6" t="n">
-        <v>0.1495002399434925</v>
+          <t>verifiedMonths[3].periodStart</t>
+        </is>
+      </c>
+      <c r="B411" s="13" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[2].month</t>
+          <t>verifiedMonths[3].periodEnd</t>
         </is>
       </c>
       <c r="B412" s="13" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-08-31</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].periodStart</t>
-        </is>
-      </c>
-      <c r="B413" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
+          <t>verifiedMonths[3].revenue</t>
+        </is>
+      </c>
+      <c r="B413" s="5" t="n">
+        <v>4232059.25</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].periodEnd</t>
-        </is>
-      </c>
-      <c r="B414" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
+          <t>verifiedMonths[3].cogs</t>
+        </is>
+      </c>
+      <c r="B414" s="5" t="n">
+        <v>2774590.65</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].revenue</t>
+          <t>verifiedMonths[3].grossProfit</t>
         </is>
       </c>
       <c r="B415" s="5" t="n">
-        <v>4593904.49</v>
+        <v>1457468.6</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].cogs</t>
+          <t>verifiedMonths[3].operatingExpenses</t>
         </is>
       </c>
       <c r="B416" s="5" t="n">
-        <v>3242912.67</v>
+        <v>851596.2</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].grossProfit</t>
+          <t>verifiedMonths[3].netIncome</t>
         </is>
       </c>
       <c r="B417" s="5" t="n">
-        <v>1350991.82</v>
+        <v>624871.9399999999</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].operatingExpenses</t>
-        </is>
-      </c>
-      <c r="B418" s="5" t="n">
-        <v>713341.59</v>
+          <t>verifiedMonths[3].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B418" s="6" t="n">
+        <v>0.3443875697156178</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].netIncome</t>
-        </is>
-      </c>
-      <c r="B419" s="5" t="n">
-        <v>677429.8100000001</v>
+          <t>verifiedMonths[3].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B419" s="6" t="n">
+        <v>0.1476519828969786</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].grossMarginPct</t>
-        </is>
-      </c>
-      <c r="B420" s="6" t="n">
-        <v>0.2940835672445598</v>
+          <t>verifiedMonths[3].month</t>
+        </is>
+      </c>
+      <c r="B420" s="13" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].netMarginPct</t>
-        </is>
-      </c>
-      <c r="B421" s="6" t="n">
-        <v>0.1474627544988424</v>
+          <t>verifiedMonths[4].periodStart</t>
+        </is>
+      </c>
+      <c r="B421" s="13" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="29" t="inlineStr">
         <is>
-          <t>verifiedMonths[3].month</t>
+          <t>verifiedMonths[4].periodEnd</t>
         </is>
       </c>
       <c r="B422" s="13" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-09-30</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="29" t="inlineStr">
         <is>
-          <t>benchmark.companyName</t>
-        </is>
-      </c>
-      <c r="B423" s="13" t="inlineStr">
-        <is>
-          <t>Midwest Design Group LLC</t>
-        </is>
+          <t>verifiedMonths[4].revenue</t>
+        </is>
+      </c>
+      <c r="B423" s="5" t="n">
+        <v>4304115.3</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="29" t="inlineStr">
         <is>
-          <t>benchmark.metricType</t>
-        </is>
-      </c>
-      <c r="B424" s="13" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
+          <t>verifiedMonths[4].cogs</t>
+        </is>
+      </c>
+      <c r="B424" s="5" t="n">
+        <v>2836553.94</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="29" t="inlineStr">
         <is>
-          <t>benchmark.metricLabel</t>
-        </is>
-      </c>
-      <c r="B425" s="13" t="inlineStr">
-        <is>
-          <t>Yearly Profit</t>
-        </is>
+          <t>verifiedMonths[4].grossProfit</t>
+        </is>
+      </c>
+      <c r="B425" s="5" t="n">
+        <v>1467561.36</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="29" t="inlineStr">
         <is>
-          <t>benchmark.metricValue</t>
+          <t>verifiedMonths[4].operatingExpenses</t>
         </is>
       </c>
       <c r="B426" s="5" t="n">
-        <v>3757685.49</v>
+        <v>803511.6800000001</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="29" t="inlineStr">
         <is>
-          <t>benchmark.regionalAverage</t>
+          <t>verifiedMonths[4].netIncome</t>
         </is>
       </c>
       <c r="B427" s="5" t="n">
-        <v>101486.51</v>
+        <v>674855.1899999999</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="29" t="inlineStr">
         <is>
-          <t>benchmark.nationalAverage</t>
-        </is>
-      </c>
-      <c r="B428" s="13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+          <t>verifiedMonths[4].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B428" s="6" t="n">
+        <v>0.3409670182394974</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="29" t="inlineStr">
         <is>
-          <t>benchmark.vsRegionalPercent</t>
-        </is>
-      </c>
-      <c r="B429" s="5" t="n">
-        <v>3602.65</v>
+          <t>verifiedMonths[4].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B429" s="6" t="n">
+        <v>0.1567930092393203</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="29" t="inlineStr">
         <is>
-          <t>benchmark.vsNationalPercent</t>
-        </is>
-      </c>
-      <c r="B430" s="6" t="n">
-        <v>0</v>
+          <t>verifiedMonths[4].month</t>
+        </is>
+      </c>
+      <c r="B430" s="13" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="29" t="inlineStr">
         <is>
-          <t>benchmark.isAboveRegional</t>
-        </is>
-      </c>
-      <c r="B431" s="6" t="b">
-        <v>1</v>
+          <t>verifiedMonths[5].periodStart</t>
+        </is>
+      </c>
+      <c r="B431" s="13" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="29" t="inlineStr">
         <is>
-          <t>benchmark.isAboveNational</t>
-        </is>
-      </c>
-      <c r="B432" s="6" t="b">
-        <v>0</v>
+          <t>verifiedMonths[5].periodEnd</t>
+        </is>
+      </c>
+      <c r="B432" s="13" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="29" t="inlineStr">
         <is>
-          <t>benchmark.location</t>
-        </is>
-      </c>
-      <c r="B433" s="13" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
+          <t>verifiedMonths[5].revenue</t>
+        </is>
+      </c>
+      <c r="B433" s="5" t="n">
+        <v>4611211.27</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="29" t="inlineStr">
         <is>
-          <t>benchmark.naicsCode</t>
-        </is>
-      </c>
-      <c r="B434" s="13" t="inlineStr">
-        <is>
-          <t>236220</t>
-        </is>
+          <t>verifiedMonths[5].cogs</t>
+        </is>
+      </c>
+      <c r="B434" s="5" t="n">
+        <v>3323848.91</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="29" t="inlineStr">
         <is>
-          <t>benchmark.industryType</t>
-        </is>
-      </c>
-      <c r="B435" s="13" t="inlineStr">
-        <is>
-          <t>Commercial And Institutional Building Construction</t>
-        </is>
+          <t>verifiedMonths[5].grossProfit</t>
+        </is>
+      </c>
+      <c r="B435" s="5" t="n">
+        <v>1287362.36</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="29" t="inlineStr">
         <is>
-          <t>benchmark.benchmarkPeriodRange</t>
-        </is>
-      </c>
-      <c r="B436" s="13" t="inlineStr">
-        <is>
-          <t>Mar 2025 - Feb 2026</t>
-        </is>
+          <t>verifiedMonths[5].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B436" s="5" t="n">
+        <v>924266.37</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="29" t="inlineStr">
         <is>
+          <t>verifiedMonths[5].netIncome</t>
+        </is>
+      </c>
+      <c r="B437" s="5" t="n">
+        <v>373967.07</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[5].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B438" s="6" t="n">
+        <v>0.2791809536846486</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[5].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B439" s="6" t="n">
+        <v>0.08109953070963921</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[5].month</t>
+        </is>
+      </c>
+      <c r="B440" s="13" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[6].periodStart</t>
+        </is>
+      </c>
+      <c r="B441" s="13" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[6].periodEnd</t>
+        </is>
+      </c>
+      <c r="B442" s="13" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[6].revenue</t>
+        </is>
+      </c>
+      <c r="B443" s="5" t="n">
+        <v>3738547.96</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[6].cogs</t>
+        </is>
+      </c>
+      <c r="B444" s="5" t="n">
+        <v>2750360.55</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[6].grossProfit</t>
+        </is>
+      </c>
+      <c r="B445" s="5" t="n">
+        <v>988187.41</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[6].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B446" s="5" t="n">
+        <v>883406.63</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[6].netIncome</t>
+        </is>
+      </c>
+      <c r="B447" s="5" t="n">
+        <v>105046.38</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[6].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B448" s="6" t="n">
+        <v>0.2643238552970176</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[6].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B449" s="6" t="n">
+        <v>0.02809817638396704</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[6].month</t>
+        </is>
+      </c>
+      <c r="B450" s="13" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[7].periodStart</t>
+        </is>
+      </c>
+      <c r="B451" s="13" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[7].periodEnd</t>
+        </is>
+      </c>
+      <c r="B452" s="13" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[7].revenue</t>
+        </is>
+      </c>
+      <c r="B453" s="5" t="n">
+        <v>4463456.92</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[7].cogs</t>
+        </is>
+      </c>
+      <c r="B454" s="5" t="n">
+        <v>2645012.62</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[7].grossProfit</t>
+        </is>
+      </c>
+      <c r="B455" s="5" t="n">
+        <v>1818444.3</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[7].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B456" s="5" t="n">
+        <v>762810.58</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[7].netIncome</t>
+        </is>
+      </c>
+      <c r="B457" s="5" t="n">
+        <v>942337.33</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[7].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B458" s="6" t="n">
+        <v>0.4074071583063469</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[7].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B459" s="6" t="n">
+        <v>0.211122756842918</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[7].month</t>
+        </is>
+      </c>
+      <c r="B460" s="13" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[8].periodStart</t>
+        </is>
+      </c>
+      <c r="B461" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[8].periodEnd</t>
+        </is>
+      </c>
+      <c r="B462" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[8].revenue</t>
+        </is>
+      </c>
+      <c r="B463" s="5" t="n">
+        <v>4471974.17</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[8].cogs</t>
+        </is>
+      </c>
+      <c r="B464" s="5" t="n">
+        <v>3167525.69</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[8].grossProfit</t>
+        </is>
+      </c>
+      <c r="B465" s="5" t="n">
+        <v>1304448.48</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[8].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B466" s="5" t="n">
+        <v>937191.25</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[8].netIncome</t>
+        </is>
+      </c>
+      <c r="B467" s="5" t="n">
+        <v>186406.72</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[8].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B468" s="6" t="n">
+        <v>0.2916940998342126</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[8].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B469" s="6" t="n">
+        <v>0.04168331768338456</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[8].month</t>
+        </is>
+      </c>
+      <c r="B470" s="13" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[9].periodStart</t>
+        </is>
+      </c>
+      <c r="B471" s="13" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[9].periodEnd</t>
+        </is>
+      </c>
+      <c r="B472" s="13" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[9].revenue</t>
+        </is>
+      </c>
+      <c r="B473" s="5" t="n">
+        <v>4949310.29</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[9].cogs</t>
+        </is>
+      </c>
+      <c r="B474" s="5" t="n">
+        <v>3687691.65</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[9].grossProfit</t>
+        </is>
+      </c>
+      <c r="B475" s="5" t="n">
+        <v>1261618.64</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[9].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B476" s="5" t="n">
+        <v>794070.1800000001</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[9].netIncome</t>
+        </is>
+      </c>
+      <c r="B477" s="5" t="n">
+        <v>468074.15</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[9].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B478" s="6" t="n">
+        <v>0.2549079702174017</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[9].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B479" s="6" t="n">
+        <v>0.09457361179106837</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[9].month</t>
+        </is>
+      </c>
+      <c r="B480" s="13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[10].periodStart</t>
+        </is>
+      </c>
+      <c r="B481" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[10].periodEnd</t>
+        </is>
+      </c>
+      <c r="B482" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[10].revenue</t>
+        </is>
+      </c>
+      <c r="B483" s="5" t="n">
+        <v>5290349.77</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[10].cogs</t>
+        </is>
+      </c>
+      <c r="B484" s="5" t="n">
+        <v>3616852.68</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[10].grossProfit</t>
+        </is>
+      </c>
+      <c r="B485" s="5" t="n">
+        <v>1673497.09</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[10].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B486" s="5" t="n">
+        <v>897079.72</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[10].netIncome</t>
+        </is>
+      </c>
+      <c r="B487" s="5" t="n">
+        <v>790908.5600000001</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[10].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B488" s="6" t="n">
+        <v>0.3163301412488649</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[10].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B489" s="6" t="n">
+        <v>0.1495002399434925</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[10].month</t>
+        </is>
+      </c>
+      <c r="B490" s="13" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[11].periodStart</t>
+        </is>
+      </c>
+      <c r="B491" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[11].periodEnd</t>
+        </is>
+      </c>
+      <c r="B492" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[11].revenue</t>
+        </is>
+      </c>
+      <c r="B493" s="5" t="n">
+        <v>4593904.49</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[11].cogs</t>
+        </is>
+      </c>
+      <c r="B494" s="5" t="n">
+        <v>3242912.67</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[11].grossProfit</t>
+        </is>
+      </c>
+      <c r="B495" s="5" t="n">
+        <v>1350991.82</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[11].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B496" s="5" t="n">
+        <v>713341.59</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[11].netIncome</t>
+        </is>
+      </c>
+      <c r="B497" s="5" t="n">
+        <v>677429.8100000001</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[11].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B498" s="6" t="n">
+        <v>0.2940835672445598</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[11].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B499" s="6" t="n">
+        <v>0.1474627544988424</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[11].month</t>
+        </is>
+      </c>
+      <c r="B500" s="13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[12].periodStart</t>
+        </is>
+      </c>
+      <c r="B501" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[12].periodEnd</t>
+        </is>
+      </c>
+      <c r="B502" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[12].revenue</t>
+        </is>
+      </c>
+      <c r="B503" s="5" t="n">
+        <v>4925779.55</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[12].cogs</t>
+        </is>
+      </c>
+      <c r="B504" s="5" t="n">
+        <v>3335298.81</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[12].grossProfit</t>
+        </is>
+      </c>
+      <c r="B505" s="5" t="n">
+        <v>1590480.74</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[12].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B506" s="5" t="n">
+        <v>978876.21</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[12].netIncome</t>
+        </is>
+      </c>
+      <c r="B507" s="5" t="n">
+        <v>611696.3100000001</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[12].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B508" s="6" t="n">
+        <v>0.3228891435062294</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[12].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B509" s="6" t="n">
+        <v>0.1241826402888859</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[12].month</t>
+        </is>
+      </c>
+      <c r="B510" s="13" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[13].periodStart</t>
+        </is>
+      </c>
+      <c r="B511" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[13].periodEnd</t>
+        </is>
+      </c>
+      <c r="B512" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[13].revenue</t>
+        </is>
+      </c>
+      <c r="B513" s="5" t="n">
+        <v>5213511.24</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[13].cogs</t>
+        </is>
+      </c>
+      <c r="B514" s="5" t="n">
+        <v>2841927.83</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[13].grossProfit</t>
+        </is>
+      </c>
+      <c r="B515" s="5" t="n">
+        <v>2371583.41</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[13].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B516" s="5" t="n">
+        <v>722028.84</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[13].netIncome</t>
+        </is>
+      </c>
+      <c r="B517" s="5" t="n">
+        <v>1649665.89</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[13].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B518" s="6" t="n">
+        <v>0.4548917803810086</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[13].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B519" s="6" t="n">
+        <v>0.3164212781096833</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[13].month</t>
+        </is>
+      </c>
+      <c r="B520" s="13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.companyName</t>
+        </is>
+      </c>
+      <c r="B521" s="13" t="inlineStr">
+        <is>
+          <t>Midwest Design Group LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricType</t>
+        </is>
+      </c>
+      <c r="B522" s="13" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricLabel</t>
+        </is>
+      </c>
+      <c r="B523" s="13" t="inlineStr">
+        <is>
+          <t>Yearly Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricValue</t>
+        </is>
+      </c>
+      <c r="B524" s="5" t="n">
+        <v>5328445.58</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.regionalAverage</t>
+        </is>
+      </c>
+      <c r="B525" s="5" t="n">
+        <v>76856.14999999999</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.nationalAverage</t>
+        </is>
+      </c>
+      <c r="B526" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.vsRegionalPercent</t>
+        </is>
+      </c>
+      <c r="B527" s="5" t="n">
+        <v>6833.01</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.vsNationalPercent</t>
+        </is>
+      </c>
+      <c r="B528" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.isAboveRegional</t>
+        </is>
+      </c>
+      <c r="B529" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.isAboveNational</t>
+        </is>
+      </c>
+      <c r="B530" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.location</t>
+        </is>
+      </c>
+      <c r="B531" s="13" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.naicsCode</t>
+        </is>
+      </c>
+      <c r="B532" s="13" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.industryType</t>
+        </is>
+      </c>
+      <c r="B533" s="13" t="inlineStr">
+        <is>
+          <t>Commercial And Institutional Building Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.benchmarkPeriodRange</t>
+        </is>
+      </c>
+      <c r="B534" s="13" t="inlineStr">
+        <is>
+          <t>May 2025 - Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="29" t="inlineStr">
+        <is>
           <t>benchmark.reportDate</t>
         </is>
       </c>
-      <c r="B437" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
+      <c r="B535" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -5829,7 +6889,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>YTD 2026 (2026-01-01 → 2026-05-07) vs FY 2025</t>
+          <t>YTD 2026 (2026-01-01 → 2026-06-30) vs FY 2025</t>
         </is>
       </c>
     </row>
@@ -5867,10 +6927,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30132990.57</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
       <c r="D5" s="5">
         <f>B5-C5</f>
@@ -5888,10 +6948,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>14108989.66</v>
+        <v>20090132.37</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>27755136.44</v>
+        <v>27754565.1</v>
       </c>
       <c r="D6" s="5">
         <f>B6-C6</f>
@@ -5952,10 +7012,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5242172.32</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>9925912.359999999</v>
+        <v>9926483.689999999</v>
       </c>
       <c r="D9" s="5">
         <f>B9-C9</f>
@@ -6032,7 +7092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6096,10 +7156,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30132990.57</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>39537774.9</v>
@@ -6120,10 +7180,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5267780.53</v>
+        <v>10042858.2</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>12736678.98</v>
+        <v>12737250.31</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>11102557.97</v>
@@ -6144,10 +7204,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.2718606082616702</v>
+        <v>0.3332844835520087</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.314549467537803</v>
+        <v>0.3145635773804887</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0.2808088719732179</v>
@@ -6164,10 +7224,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5242172.32</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>9925912.359999999</v>
+        <v>9926483.689999999</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>8249044.14</v>
@@ -6188,7 +7248,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4800685.88</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>2810766.62</v>
@@ -6212,10 +7272,10 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.08575153308354315</v>
+        <v>0.15931660911146</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.06941567304022843</v>
+        <v>0.06941567305737158</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>0.07332639652415061</v>
@@ -6341,14 +7401,14 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>5290349.77</v>
+        <v>3347154.03</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>3616852.68</v>
+        <v>1995316.63</v>
       </c>
       <c r="D17" s="5">
         <f>B17-C17</f>
@@ -6359,7 +7419,7 @@
         <v/>
       </c>
       <c r="F17" s="5" t="n">
-        <v>897079.72</v>
+        <v>879964.46</v>
       </c>
       <c r="G17" s="5">
         <f>D17-F17</f>
@@ -6373,14 +7433,14 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>4593904.49</v>
+        <v>4232059.25</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>3242912.67</v>
+        <v>2774590.65</v>
       </c>
       <c r="D18" s="5">
         <f>B18-C18</f>
@@ -6391,7 +7451,7 @@
         <v/>
       </c>
       <c r="F18" s="5" t="n">
-        <v>713341.59</v>
+        <v>851596.2</v>
       </c>
       <c r="G18" s="5">
         <f>D18-F18</f>
@@ -6399,6 +7459,326 @@
       </c>
       <c r="H18" s="6">
         <f>IFERROR(G18/B18,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4304115.3</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2836553.94</v>
+      </c>
+      <c r="D19" s="5">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="6">
+        <f>IFERROR(D19/B19,0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>803511.6800000001</v>
+      </c>
+      <c r="G19" s="5">
+        <f>D19-F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="6">
+        <f>IFERROR(G19/B19,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>4611211.27</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>3323848.91</v>
+      </c>
+      <c r="D20" s="5">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="6">
+        <f>IFERROR(D20/B20,0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>924266.37</v>
+      </c>
+      <c r="G20" s="5">
+        <f>D20-F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="6">
+        <f>IFERROR(G20/B20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3738547.96</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2750360.55</v>
+      </c>
+      <c r="D21" s="5">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="6">
+        <f>IFERROR(D21/B21,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>883406.63</v>
+      </c>
+      <c r="G21" s="5">
+        <f>D21-F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="6">
+        <f>IFERROR(G21/B21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>4463456.92</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2645012.62</v>
+      </c>
+      <c r="D22" s="5">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="6">
+        <f>IFERROR(D22/B22,0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>762810.58</v>
+      </c>
+      <c r="G22" s="5">
+        <f>D22-F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="6">
+        <f>IFERROR(G22/B22,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>4471974.17</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>3167525.69</v>
+      </c>
+      <c r="D23" s="5">
+        <f>B23-C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="6">
+        <f>IFERROR(D23/B23,0)</f>
+        <v/>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>937191.25</v>
+      </c>
+      <c r="G23" s="5">
+        <f>D23-F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="6">
+        <f>IFERROR(G23/B23,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>4949310.29</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>3687691.65</v>
+      </c>
+      <c r="D24" s="5">
+        <f>B24-C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="6">
+        <f>IFERROR(D24/B24,0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>794070.1800000001</v>
+      </c>
+      <c r="G24" s="5">
+        <f>D24-F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="6">
+        <f>IFERROR(G24/B24,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>5290349.77</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>3616852.68</v>
+      </c>
+      <c r="D25" s="5">
+        <f>B25-C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="6">
+        <f>IFERROR(D25/B25,0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>897079.72</v>
+      </c>
+      <c r="G25" s="5">
+        <f>D25-F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="6">
+        <f>IFERROR(G25/B25,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>4593904.49</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>3242912.67</v>
+      </c>
+      <c r="D26" s="5">
+        <f>B26-C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="6">
+        <f>IFERROR(D26/B26,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>713341.59</v>
+      </c>
+      <c r="G26" s="5">
+        <f>D26-F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="6">
+        <f>IFERROR(G26/B26,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4925779.55</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>3335298.81</v>
+      </c>
+      <c r="D27" s="5">
+        <f>B27-C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="6">
+        <f>IFERROR(D27/B27,0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>978876.21</v>
+      </c>
+      <c r="G27" s="5">
+        <f>D27-F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="6">
+        <f>IFERROR(G27/B27,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5213511.24</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>2841927.83</v>
+      </c>
+      <c r="D28" s="5">
+        <f>B28-C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="6">
+        <f>IFERROR(D28/B28,0)</f>
+        <v/>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>722028.84</v>
+      </c>
+      <c r="G28" s="5">
+        <f>D28-F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="6">
+        <f>IFERROR(G28/B28,0)</f>
         <v/>
       </c>
     </row>
@@ -6469,10 +7849,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30132990.57</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
       <c r="D6" s="5">
         <f>B6-C6</f>
@@ -6486,10 +7866,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>14108989.66</v>
+        <v>20090132.37</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>27755136.44</v>
+        <v>27754565.1</v>
       </c>
       <c r="D7" s="5">
         <f>B7-C7</f>
@@ -6503,10 +7883,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>5267780.53</v>
+        <v>10042858.2</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>12736678.98</v>
+        <v>12737250.31</v>
       </c>
       <c r="D8" s="5">
         <f>B8-C8</f>
@@ -6520,10 +7900,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.2718606082616702</v>
+        <v>0.3332844835520087</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.314549467537803</v>
+        <v>0.3145635773804887</v>
       </c>
       <c r="D9" s="6">
         <f>B9-C9</f>
@@ -6537,10 +7917,10 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5242172.32</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>9925912.359999999</v>
+        <v>9926483.689999999</v>
       </c>
       <c r="D10" s="5">
         <f>B10-C10</f>
@@ -6554,7 +7934,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4800685.88</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>2810766.62</v>
@@ -6600,7 +7980,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>760034.3</v>
+        <v>856166.26</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>1607367.49</v>
@@ -6634,7 +8014,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>-1330991.51</v>
+        <v>-1717084.83</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>-1432655.18</v>
@@ -6733,7 +8113,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5 of 12 months completed · 7 remaining. Year-End Forecast = YTD + (Avg Monthly × Remaining).</t>
+          <t>6 of 12 months completed · 6 remaining. Year-End Forecast = YTD + (Avg Monthly × Remaining).</t>
         </is>
       </c>
     </row>
@@ -6771,13 +8151,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30132990.57</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3875354.04</v>
+        <v>5022165.09</v>
       </c>
       <c r="D5" s="5">
-        <f>B5+C5*7</f>
+        <f>B5+C5*6</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -6792,13 +8172,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5267780.53</v>
+        <v>10042858.2</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1053556.11</v>
+        <v>1673809.7</v>
       </c>
       <c r="D6" s="5">
-        <f>B6+C6*7</f>
+        <f>B6+C6*6</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -6813,13 +8193,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5242172.32</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>696027.75</v>
+        <v>873695.39</v>
       </c>
       <c r="D7" s="5">
-        <f>B7+C7*7</f>
+        <f>B7+C7*6</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -6834,13 +8214,13 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4800685.88</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>332317.55</v>
+        <v>800114.3100000001</v>
       </c>
       <c r="D8" s="5">
-        <f>B8+C8*7</f>
+        <f>B8+C8*6</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -6877,7 +8257,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-1103389.81</v>
+        <v>-1540070.49</v>
       </c>
     </row>
   </sheetData>
@@ -6895,7 +8275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6983,19 +8363,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>12736678.98</v>
+        <v>12737250.31</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.314549467537803</v>
+        <v>0.3145635773804887</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>2810766.62</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.06941567304022843</v>
+        <v>0.06941567305737158</v>
       </c>
     </row>
     <row r="7">
@@ -7005,19 +8385,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30132990.57</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>5267780.53</v>
+        <v>10042858.2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.2718606082616702</v>
+        <v>0.3332844835520087</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4800685.88</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.08575153308354315</v>
+        <v>0.15931660911146</v>
       </c>
     </row>
     <row r="8">
@@ -7027,19 +8407,19 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>46504248.46</v>
+        <v>60265981.14</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>12642673.27</v>
+        <v>20085716.4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.2718606081952797</v>
+        <v>0.3332844835520087</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3987810.6</v>
+        <v>9601371.76</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.08575153307616747</v>
+        <v>0.15931660911146</v>
       </c>
     </row>
     <row r="11">
@@ -7150,57 +8530,337 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>5290349.77</v>
+        <v>3347154.03</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3616852.68</v>
+        <v>1995316.63</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1673497.09</v>
+        <v>1351837.4</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>897079.72</v>
+        <v>879964.46</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>790908.5600000001</v>
+        <v>597004.63</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.3163301412488649</v>
+        <v>0.4038766629452065</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.1495002399434925</v>
+        <v>0.1783618634365624</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>4232059.25</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2774590.65</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1457468.6</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>851596.2</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>624871.9399999999</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.3443875697156178</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1476519828969786</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>4304115.3</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2836553.94</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1467561.36</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>803511.6800000001</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>674855.1899999999</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0.3409670182394974</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.1567930092393203</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>4611211.27</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3323848.91</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1287362.36</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>924266.37</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>373967.07</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2791809536846486</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.08109953070963921</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3738547.96</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2750360.55</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>988187.41</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>883406.63</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>105046.38</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.2643238552970176</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.02809817638396704</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>4463456.92</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>2645012.62</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1818444.3</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>762810.58</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>942337.33</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.4074071583063469</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.211122756842918</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>4471974.17</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3167525.69</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1304448.48</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>937191.25</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>186406.72</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.2916940998342126</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.04168331768338456</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>4949310.29</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>3687691.65</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1261618.64</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>794070.1800000001</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>468074.15</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.2549079702174017</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.09457361179106837</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>5290349.77</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>3616852.68</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1673497.09</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>897079.72</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>790908.5600000001</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0.3163301412488649</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0.1495002399434925</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B24" s="5" t="n">
         <v>4593904.49</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C24" s="5" t="n">
         <v>3242912.67</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D24" s="5" t="n">
         <v>1350991.82</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E24" s="5" t="n">
         <v>713341.59</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F24" s="5" t="n">
         <v>677429.8100000001</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G24" s="6" t="n">
         <v>0.2940835672445598</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H24" s="6" t="n">
         <v>0.1474627544988424</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>4925779.55</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>3335298.81</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1590480.74</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>978876.21</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>611696.3100000001</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.3228891435062294</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.1241826402888859</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>5213511.24</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>2841927.83</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>2371583.41</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>722028.84</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>1649665.89</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0.4548917803810086</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.3164212781096833</v>
       </c>
     </row>
   </sheetData>
@@ -7281,7 +8941,7 @@
         <v>20720.33</v>
       </c>
       <c r="C6" s="6">
-        <f>B6/19376770.19</f>
+        <f>B6/30132990.57</f>
         <v/>
       </c>
       <c r="D6" s="5" t="n">
@@ -7295,10 +8955,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>571765.41</v>
+        <v>954478.7</v>
       </c>
       <c r="C7" s="6">
-        <f>B7/19376770.19</f>
+        <f>B7/30132990.57</f>
         <v/>
       </c>
       <c r="D7" s="5" t="n">
@@ -7312,10 +8972,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>16823.83</v>
+        <v>16826.61</v>
       </c>
       <c r="C8" s="6">
-        <f>B8/19376770.19</f>
+        <f>B8/30132990.57</f>
         <v/>
       </c>
       <c r="D8" s="5" t="n">
@@ -7329,10 +8989,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>206725</v>
+        <v>396425</v>
       </c>
       <c r="C9" s="6">
-        <f>B9/19376770.19</f>
+        <f>B9/30132990.57</f>
         <v/>
       </c>
       <c r="D9" s="5" t="n">
@@ -7349,7 +9009,7 @@
         <v>4820</v>
       </c>
       <c r="C10" s="6">
-        <f>B10/19376770.19</f>
+        <f>B10/30132990.57</f>
         <v/>
       </c>
       <c r="D10" s="5" t="n">
@@ -7363,14 +9023,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>15924134.62</v>
+        <v>25713723.99</v>
       </c>
       <c r="C11" s="6">
-        <f>B11/19376770.19</f>
+        <f>B11/30132990.57</f>
         <v/>
       </c>
       <c r="D11" s="5" t="n">
-        <v>33721642.66</v>
+        <v>33721642.65</v>
       </c>
     </row>
     <row r="12">
@@ -7380,10 +9040,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>2347599</v>
+        <v>2544448.44</v>
       </c>
       <c r="C12" s="6">
-        <f>B12/19376770.19</f>
+        <f>B12/30132990.57</f>
         <v/>
       </c>
       <c r="D12" s="5" t="n">
@@ -7426,10 +9086,10 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>6261029.85</v>
+        <v>8677589.449999999</v>
       </c>
       <c r="C17" s="6">
-        <f>B17/14108989.66</f>
+        <f>B17/20090132.37</f>
         <v/>
       </c>
       <c r="D17" s="5" t="n">
@@ -7443,10 +9103,10 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>2745051.1</v>
+        <v>3879854.77</v>
       </c>
       <c r="C18" s="6">
-        <f>B18/14108989.66</f>
+        <f>B18/20090132.37</f>
         <v/>
       </c>
       <c r="D18" s="5" t="n">
@@ -7460,10 +9120,10 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>529849.5</v>
+        <v>781598.96</v>
       </c>
       <c r="C19" s="6">
-        <f>B19/14108989.66</f>
+        <f>B19/20090132.37</f>
         <v/>
       </c>
       <c r="D19" s="5" t="n">
@@ -7511,10 +9171,10 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1928101.09</v>
+        <v>2916068.14</v>
       </c>
       <c r="C24" s="6">
-        <f>B24/3480138.73</f>
+        <f>B24/5242172.32</f>
         <v/>
       </c>
       <c r="D24" s="5" t="n">
@@ -7532,14 +9192,14 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>757455.8100000001</v>
+        <v>990801.9300000001</v>
       </c>
       <c r="C25" s="6">
-        <f>B25/3480138.73</f>
+        <f>B25/5242172.32</f>
         <v/>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1286006.54</v>
+        <v>196030.17</v>
       </c>
       <c r="E25" s="6">
         <f>IFERROR((B25-D25)/ABS(D25),"")</f>
@@ -7553,10 +9213,10 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>72850.52</v>
+        <v>139047.64</v>
       </c>
       <c r="C26" s="6">
-        <f>B26/3480138.73</f>
+        <f>B26/5242172.32</f>
         <v/>
       </c>
       <c r="D26" s="5" t="n">
@@ -7574,10 +9234,10 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>191337.16</v>
+        <v>317740.36</v>
       </c>
       <c r="C27" s="6">
-        <f>B27/3480138.73</f>
+        <f>B27/5242172.32</f>
         <v/>
       </c>
       <c r="D27" s="5" t="n">
@@ -7595,10 +9255,10 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>64541.24</v>
+        <v>134589.28</v>
       </c>
       <c r="C28" s="6">
-        <f>B28/3480138.73</f>
+        <f>B28/5242172.32</f>
         <v/>
       </c>
       <c r="D28" s="5" t="n">
@@ -7616,14 +9276,14 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>221218.59</v>
+        <v>402320.28</v>
       </c>
       <c r="C29" s="6">
-        <f>B29/3480138.73</f>
+        <f>B29/5242172.32</f>
         <v/>
       </c>
       <c r="D29" s="5" t="n">
-        <v>981759.21</v>
+        <v>981248.3100000001</v>
       </c>
       <c r="E29" s="6">
         <f>IFERROR((B29-D29)/ABS(D29),"")</f>
@@ -7703,7 +9363,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>-649262.0699999999</v>
+        <v>-1802279.03</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>-733947.11</v>
@@ -7725,7 +9385,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>286831.19</v>
+        <v>933211.54</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>712464.46</v>
@@ -7747,7 +9407,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-837450.48</v>
+        <v>-1178924.86</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>-2438809.88</v>
@@ -7769,7 +9429,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>193111.88</v>
+        <v>84158.12</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>362396.12</v>
@@ -7791,7 +9451,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>-1073267.83</v>
+        <v>-563772.95</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>1249606.34</v>
@@ -7813,7 +9473,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>-1274331.17</v>
+        <v>-1980675.49</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>215079.93</v>
@@ -7835,7 +9495,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2536373.04</v>
+        <v>545048.77</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>-460964.34</v>
@@ -7917,7 +9577,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30132990.57</v>
       </c>
     </row>
     <row r="6">
@@ -7986,10 +9646,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>46504248.46</v>
+        <v>60265981.14</v>
       </c>
       <c r="C12" s="5">
-        <f>B5+(3875354.04*7)*(1+$B$6)</f>
+        <f>B5+(5022165.09*6)*(1+$B$6)</f>
         <v/>
       </c>
       <c r="D12" s="5">
@@ -8004,10 +9664,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.2718606081952797</v>
+        <v>0.3332844835520087</v>
       </c>
       <c r="C13" s="6">
-        <f>0.2718606081952797+$B$7</f>
+        <f>0.33328448355200874+$B$7</f>
         <v/>
       </c>
       <c r="D13" s="6">
@@ -8022,7 +9682,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>12642673.27</v>
+        <v>20085716.4</v>
       </c>
       <c r="C14" s="5">
         <f>C12*C13</f>
@@ -8040,10 +9700,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>8352332.95</v>
+        <v>10484344.64</v>
       </c>
       <c r="C15" s="5">
-        <f>3480138.73+(696027.75*7)*(1+$B$8)</f>
+        <f>5242172.32+(873695.39*6)*(1+$B$8)</f>
         <v/>
       </c>
       <c r="D15" s="5">
@@ -8058,7 +9718,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>3987810.6</v>
+        <v>9601371.76</v>
       </c>
       <c r="C16" s="5">
         <f>C14-C15</f>
@@ -8076,7 +9736,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.08575153307616747</v>
+        <v>0.15931660911146</v>
       </c>
       <c r="C17" s="6">
         <f>C16/C12</f>

--- a/cfo-dashboard/downloads/cfo-dashboard.xlsx
+++ b/cfo-dashboard/downloads/cfo-dashboard.xlsx
@@ -612,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Commercial and Institutional Building Construction (NAICS 236220)  ·  As of 2026-05-07  ·  Source: QuickBooks Online (live, via QuickBooks MCP)</t>
+          <t>Commercial and Institutional Building Construction (NAICS 236220)  ·  As of 2026-07-07  ·  Source: QuickBooks Online (live, via QuickBooks MCP)</t>
         </is>
       </c>
     </row>
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30240248.32</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
       <c r="D5" s="5">
         <f>B5-C5</f>
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5267780.53</v>
+        <v>9948089.85</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>12736678.98</v>
+        <v>12737250.31</v>
       </c>
       <c r="D6" s="5">
         <f>B6-C6</f>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.2718606082616702</v>
+        <v>0.3289685238272541</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.314549467537803</v>
+        <v>0.3145635773804887</v>
       </c>
       <c r="D7" s="6">
         <f>B7-C7</f>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5403991.67</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>9925912.359999999</v>
+        <v>9926483.689999999</v>
       </c>
       <c r="D8" s="5">
         <f>B8-C8</f>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4544098.18</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>2810766.62</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.08575153308354315</v>
+        <v>0.1502665630227206</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.06941567304022843</v>
+        <v>0.06941567305737158</v>
       </c>
       <c r="D10" s="6">
         <f>B10-C10</f>
@@ -1010,29 +1010,29 @@
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t>Run-rate $46,504,248 vs FY 2025 $40,491,815.</t>
+          <t>Run-rate $51,840,426 vs FY 2025 $40,491,815.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>Gross margin compression vs prior year</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>BAD</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Gross margin expansion vs prior year</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
-        <is>
-          <t>GM% 27.19% vs prior 31.45% (-4.27pt).</t>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>GM% 32.90% vs prior 31.46% (+1.44pt).</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18T00:24:51.804946+00:00</t>
+          <t>2026-07-07T17:35:42.805909+00:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30240248.32</v>
       </c>
     </row>
     <row r="55">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>14108989.66</v>
+        <v>20292158.47</v>
       </c>
     </row>
     <row r="56">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>5267780.53</v>
+        <v>9948089.85</v>
       </c>
     </row>
     <row r="57">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5403991.67</v>
       </c>
     </row>
     <row r="58">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4544098.18</v>
       </c>
     </row>
     <row r="59">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>0.2718606082616702</v>
+        <v>0.3289685238272541</v>
       </c>
     </row>
     <row r="60">
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="B60" s="6" t="n">
-        <v>0.08575153308354315</v>
+        <v>0.1502665630227206</v>
       </c>
     </row>
     <row r="61">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>571765.41</v>
+        <v>997500.28</v>
       </c>
     </row>
     <row r="65">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="B66" s="5" t="n">
-        <v>16823.83</v>
+        <v>16826.61</v>
       </c>
     </row>
     <row r="67">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B68" s="5" t="n">
-        <v>206725</v>
+        <v>396425</v>
       </c>
     </row>
     <row r="69">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>15924134.62</v>
+        <v>25762267.87</v>
       </c>
     </row>
     <row r="73">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>2347599</v>
+        <v>2544448.44</v>
       </c>
     </row>
     <row r="75">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>6261029.85</v>
+        <v>8828741.710000001</v>
       </c>
     </row>
     <row r="77">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>2745051.1</v>
+        <v>3895643.04</v>
       </c>
     </row>
     <row r="79">
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="B80" s="5" t="n">
-        <v>529849.5</v>
+        <v>799947.42</v>
       </c>
     </row>
     <row r="81">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B82" s="5" t="n">
-        <v>1928101.09</v>
+        <v>2918142.76</v>
       </c>
     </row>
     <row r="83">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>757455.8100000001</v>
+        <v>1109860.58</v>
       </c>
     </row>
     <row r="85">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>72850.52</v>
+        <v>139754.06</v>
       </c>
     </row>
     <row r="87">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>191337.16</v>
+        <v>357720.02</v>
       </c>
     </row>
     <row r="89">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="B90" s="5" t="n">
-        <v>64541.24</v>
+        <v>134589.28</v>
       </c>
     </row>
     <row r="91">
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>221218.59</v>
+        <v>402320.28</v>
       </c>
     </row>
     <row r="93">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="B95" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
     </row>
     <row r="96">
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="B96" s="5" t="n">
-        <v>27755136.44</v>
+        <v>27754565.1</v>
       </c>
     </row>
     <row r="97">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="B97" s="5" t="n">
-        <v>12736678.98</v>
+        <v>12737250.31</v>
       </c>
     </row>
     <row r="98">
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="B98" s="5" t="n">
-        <v>9925912.359999999</v>
+        <v>9926483.689999999</v>
       </c>
     </row>
     <row r="99">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="B100" s="6" t="n">
-        <v>0.314549467537803</v>
+        <v>0.3145635773804887</v>
       </c>
     </row>
     <row r="101">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>0.06941567304022843</v>
+        <v>0.06941567305737158</v>
       </c>
     </row>
     <row r="102">
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="B127" s="5" t="n">
-        <v>33721642.66</v>
+        <v>33721642.65</v>
       </c>
     </row>
     <row r="128">
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="B143" s="5" t="n">
-        <v>1286006.54</v>
+        <v>196030.17</v>
       </c>
     </row>
     <row r="144">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="B151" s="5" t="n">
-        <v>981759.21</v>
+        <v>981248.3100000001</v>
       </c>
     </row>
     <row r="152">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="B219" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="B220" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221">
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="B221" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30240248.32</v>
       </c>
     </row>
     <row r="222">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="B222" s="5" t="n">
-        <v>5267780.53</v>
+        <v>9948089.85</v>
       </c>
     </row>
     <row r="223">
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="B223" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5403991.67</v>
       </c>
     </row>
     <row r="224">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="B224" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4544098.18</v>
       </c>
     </row>
     <row r="225">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="B225" s="5" t="n">
-        <v>3875354.04</v>
+        <v>4320035.47</v>
       </c>
     </row>
     <row r="226">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="B226" s="5" t="n">
-        <v>1053556.11</v>
+        <v>1421155.69</v>
       </c>
     </row>
     <row r="227">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="B227" s="5" t="n">
-        <v>696027.75</v>
+        <v>771998.8100000001</v>
       </c>
     </row>
     <row r="228">
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="B228" s="5" t="n">
-        <v>332317.55</v>
+        <v>649156.88</v>
       </c>
     </row>
     <row r="229">
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="B229" s="5" t="n">
-        <v>46504248.46</v>
+        <v>51840425.69</v>
       </c>
     </row>
     <row r="230">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="B230" s="5" t="n">
-        <v>12642673.27</v>
+        <v>17053868.31</v>
       </c>
     </row>
     <row r="231">
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="B231" s="5" t="n">
-        <v>8352332.95</v>
+        <v>9263985.720000001</v>
       </c>
     </row>
     <row r="232">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="B232" s="5" t="n">
-        <v>3987810.6</v>
+        <v>7789882.59</v>
       </c>
     </row>
     <row r="233">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="B233" s="5" t="n">
-        <v>46504248.46</v>
+        <v>51840425.69</v>
       </c>
     </row>
     <row r="234">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="B234" s="5" t="n">
-        <v>12642673.27</v>
+        <v>17053868.31</v>
       </c>
     </row>
     <row r="235">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="B235" s="5" t="n">
-        <v>8352332.95</v>
+        <v>9263985.720000001</v>
       </c>
     </row>
     <row r="236">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="B236" s="5" t="n">
-        <v>3987810.6</v>
+        <v>7789882.59</v>
       </c>
     </row>
     <row r="237">
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="B237" s="6" t="n">
-        <v>0.2718606081952797</v>
+        <v>0.3289685237536482</v>
       </c>
     </row>
     <row r="238">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="B238" s="6" t="n">
-        <v>0.08575153307616747</v>
+        <v>0.1502665629441902</v>
       </c>
     </row>
     <row r="239">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="B239" s="5" t="n">
-        <v>-1103389.81</v>
+        <v>-857832.02</v>
       </c>
     </row>
     <row r="240">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="B240" s="5" t="n">
-        <v>1824082.32</v>
+        <v>1302915.94</v>
       </c>
     </row>
     <row r="241">
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="B244" s="5" t="n">
-        <v>46504248.46</v>
+        <v>51840425.69</v>
       </c>
     </row>
     <row r="245">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B245" s="13" t="inlineStr">
         <is>
-          <t>YTD avg monthly $3,875,354 continues for 7 months</t>
+          <t>YTD avg monthly $4,320,035 continues for 5 months</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="B249" s="5" t="n">
-        <v>47158830.4</v>
+        <v>52361634.69</v>
       </c>
     </row>
     <row r="250">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B250" s="13" t="inlineStr">
         <is>
-          <t>Apply prior-year YoY growth +2.4% to remaining 7 months</t>
+          <t>Apply prior-year YoY growth +2.4% to remaining 5 months</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="B251" s="6" t="n">
-        <v>0.02412984854137568</v>
+        <v>0.02412984828845288</v>
       </c>
     </row>
     <row r="252">
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="B255" s="5" t="n">
-        <v>42996995.85</v>
+        <v>47111838.07</v>
       </c>
     </row>
     <row r="256">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="B256" s="13" t="inlineStr">
         <is>
-          <t>YTD actual + prior-year avg monthly $3,374,318 × 7 remaining months</t>
+          <t>YTD actual + prior-year avg monthly $3,374,318 × 5 remaining months</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="B260" s="5" t="n">
-        <v>52919774.6</v>
+        <v>67632178.84999999</v>
       </c>
     </row>
     <row r="261">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="B261" s="5" t="n">
-        <v>44902063.06</v>
+        <v>36770346.65</v>
       </c>
     </row>
     <row r="262">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="B262" s="13" t="inlineStr">
         <is>
-          <t>Avg billings $4,065,858/mo × 7 remaining + YTD; recognized at YTD billings→revenue ratio of 1.18</t>
+          <t>Avg billings $4,065,858/mo × 5 remaining + YTD; recognized at YTD billings→revenue ratio of 1.84</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="B263" s="5" t="n">
-        <v>1.178559981161696</v>
+        <v>1.839313060993898</v>
       </c>
     </row>
     <row r="264">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="B267" s="5" t="n">
-        <v>47394962.33</v>
+        <v>54736519.32</v>
       </c>
     </row>
     <row r="268">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="B268" s="5" t="n">
-        <v>42996995.85</v>
+        <v>47111838.07</v>
       </c>
     </row>
     <row r="269">
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="B269" s="5" t="n">
-        <v>52919774.6</v>
+        <v>67632178.84999999</v>
       </c>
     </row>
     <row r="270">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="B270" s="5" t="n">
-        <v>9922778.75</v>
+        <v>20520340.78</v>
       </c>
     </row>
     <row r="271">
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="B272" s="5" t="n">
-        <v>46504248.46</v>
+        <v>51840425.69</v>
       </c>
     </row>
     <row r="273">
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="B273" s="6" t="n">
-        <v>0.2718606081952797</v>
+        <v>0.3289685237536482</v>
       </c>
     </row>
     <row r="274">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="B274" s="6" t="n">
-        <v>0.08575153307616747</v>
+        <v>0.1502665629441902</v>
       </c>
     </row>
     <row r="275">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B275" s="6" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.1451</v>
       </c>
     </row>
     <row r="276">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="B277" s="6" t="n">
-        <v>0.0345</v>
+        <v>0.0951</v>
       </c>
     </row>
     <row r="278">
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="B280" s="5" t="n">
-        <v>48109881.41</v>
+        <v>56768366.09</v>
       </c>
     </row>
     <row r="281">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="B281" s="5" t="n">
-        <v>12116983.99</v>
+        <v>17539638.27</v>
       </c>
     </row>
     <row r="282">
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="B282" s="6" t="n">
-        <v>0.2518606081952797</v>
+        <v>0.3089685237536482</v>
       </c>
     </row>
     <row r="283">
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="B283" s="5" t="n">
-        <v>3451957.75</v>
+        <v>7735630.13</v>
       </c>
     </row>
     <row r="284">
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="B284" s="6" t="n">
-        <v>0.07175153307616747</v>
+        <v>0.1362665629441902</v>
       </c>
     </row>
     <row r="285">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="B286" s="5" t="n">
-        <v>49770951.38</v>
+        <v>62164755.51</v>
       </c>
     </row>
     <row r="287">
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="B287" s="5" t="n">
-        <v>11539923.06</v>
+        <v>17963657.63</v>
       </c>
     </row>
     <row r="288">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="B288" s="6" t="n">
-        <v>0.2318606081952797</v>
+        <v>0.2889685237536482</v>
       </c>
     </row>
     <row r="289">
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="B289" s="5" t="n">
-        <v>2874348.75</v>
+        <v>7600670.99</v>
       </c>
     </row>
     <row r="290">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="B290" s="6" t="n">
-        <v>0.05775153307616747</v>
+        <v>0.1222665629441902</v>
       </c>
     </row>
     <row r="291">
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="B292" s="6" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.1451</v>
       </c>
     </row>
     <row r="293">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="B295" s="5" t="n">
-        <v>50435093.83</v>
+        <v>59360387.37</v>
       </c>
     </row>
     <row r="296">
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="B296" s="5" t="n">
-        <v>13711315.28</v>
+        <v>19527699</v>
       </c>
     </row>
     <row r="297">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="B297" s="6" t="n">
-        <v>0.2718606081952797</v>
+        <v>0.3289685237536482</v>
       </c>
     </row>
     <row r="298">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="B298" s="5" t="n">
-        <v>4324886.62</v>
+        <v>8919881.390000001</v>
       </c>
     </row>
     <row r="299">
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="B299" s="6" t="n">
-        <v>0.08575153307616747</v>
+        <v>0.1502665629441902</v>
       </c>
     </row>
     <row r="300">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="B301" s="5" t="n">
-        <v>54698200.15</v>
+        <v>67971193.18000001</v>
       </c>
     </row>
     <row r="302">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="B302" s="5" t="n">
-        <v>14870285.96</v>
+        <v>22360383.08</v>
       </c>
     </row>
     <row r="303">
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="B303" s="6" t="n">
-        <v>0.2718606081952797</v>
+        <v>0.3289685237536482</v>
       </c>
     </row>
     <row r="304">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="B304" s="5" t="n">
-        <v>4690454.52</v>
+        <v>10213797.58</v>
       </c>
     </row>
     <row r="305">
@@ -4389,7 +4389,7 @@
         </is>
       </c>
       <c r="B305" s="6" t="n">
-        <v>0.08575153307616747</v>
+        <v>0.1502665629441902</v>
       </c>
     </row>
     <row r="306">
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="B307" s="6" t="n">
-        <v>0.1245</v>
+        <v>0.1851</v>
       </c>
     </row>
     <row r="308">
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="B310" s="5" t="n">
-        <v>52295263.77</v>
+        <v>61434004.4</v>
       </c>
     </row>
     <row r="311">
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="B311" s="5" t="n">
-        <v>15001451.17</v>
+        <v>21131363.8</v>
       </c>
     </row>
     <row r="312">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="B312" s="6" t="n">
-        <v>0.2868606081952797</v>
+        <v>0.3439685237536482</v>
       </c>
     </row>
     <row r="313">
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="B313" s="5" t="n">
-        <v>5033499.31</v>
+        <v>9876533.74</v>
       </c>
     </row>
     <row r="314">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="B314" s="6" t="n">
-        <v>0.09625153307616746</v>
+        <v>0.1607665629441902</v>
       </c>
     </row>
     <row r="315">
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="B316" s="5" t="n">
-        <v>58807414.45</v>
+        <v>72802968.84999999</v>
       </c>
     </row>
     <row r="317">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="B317" s="5" t="n">
-        <v>17751641.89</v>
+        <v>26133974.25</v>
       </c>
     </row>
     <row r="318">
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="B318" s="6" t="n">
-        <v>0.3018606081952797</v>
+        <v>0.3589685237536482</v>
       </c>
     </row>
     <row r="319">
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="B319" s="5" t="n">
-        <v>6277781.65</v>
+        <v>12468714.25</v>
       </c>
     </row>
     <row r="320">
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="B320" s="6" t="n">
-        <v>0.1067515330761675</v>
+        <v>0.1712665629441902</v>
       </c>
     </row>
     <row r="321">
@@ -5629,166 +5629,378 @@
     <row r="423">
       <c r="A423" s="29" t="inlineStr">
         <is>
-          <t>benchmark.companyName</t>
+          <t>verifiedMonths[4].periodStart</t>
         </is>
       </c>
       <c r="B423" s="13" t="inlineStr">
         <is>
-          <t>Midwest Design Group LLC</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="29" t="inlineStr">
         <is>
-          <t>benchmark.metricType</t>
+          <t>verifiedMonths[4].periodEnd</t>
         </is>
       </c>
       <c r="B424" s="13" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="29" t="inlineStr">
         <is>
-          <t>benchmark.metricLabel</t>
-        </is>
-      </c>
-      <c r="B425" s="13" t="inlineStr">
-        <is>
-          <t>Yearly Profit</t>
-        </is>
+          <t>verifiedMonths[4].revenue</t>
+        </is>
+      </c>
+      <c r="B425" s="5" t="n">
+        <v>4925779.55</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="29" t="inlineStr">
         <is>
-          <t>benchmark.metricValue</t>
+          <t>verifiedMonths[4].cogs</t>
         </is>
       </c>
       <c r="B426" s="5" t="n">
-        <v>3757685.49</v>
+        <v>3335298.81</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="29" t="inlineStr">
         <is>
-          <t>benchmark.regionalAverage</t>
+          <t>verifiedMonths[4].grossProfit</t>
         </is>
       </c>
       <c r="B427" s="5" t="n">
-        <v>101486.51</v>
+        <v>1590480.74</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="29" t="inlineStr">
         <is>
-          <t>benchmark.nationalAverage</t>
-        </is>
-      </c>
-      <c r="B428" s="13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+          <t>verifiedMonths[4].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B428" s="5" t="n">
+        <v>978876.21</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="29" t="inlineStr">
         <is>
-          <t>benchmark.vsRegionalPercent</t>
+          <t>verifiedMonths[4].netIncome</t>
         </is>
       </c>
       <c r="B429" s="5" t="n">
-        <v>3602.65</v>
+        <v>611696.3100000001</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="29" t="inlineStr">
         <is>
-          <t>benchmark.vsNationalPercent</t>
+          <t>verifiedMonths[4].grossMarginPct</t>
         </is>
       </c>
       <c r="B430" s="6" t="n">
-        <v>0</v>
+        <v>0.3228891435062294</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="29" t="inlineStr">
         <is>
-          <t>benchmark.isAboveRegional</t>
-        </is>
-      </c>
-      <c r="B431" s="6" t="b">
-        <v>1</v>
+          <t>verifiedMonths[4].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B431" s="6" t="n">
+        <v>0.1241826402888859</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="29" t="inlineStr">
         <is>
-          <t>benchmark.isAboveNational</t>
-        </is>
-      </c>
-      <c r="B432" s="6" t="b">
-        <v>0</v>
+          <t>verifiedMonths[4].month</t>
+        </is>
+      </c>
+      <c r="B432" s="13" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="29" t="inlineStr">
         <is>
-          <t>benchmark.location</t>
+          <t>verifiedMonths[5].periodStart</t>
         </is>
       </c>
       <c r="B433" s="13" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="29" t="inlineStr">
         <is>
-          <t>benchmark.naicsCode</t>
+          <t>verifiedMonths[5].periodEnd</t>
         </is>
       </c>
       <c r="B434" s="13" t="inlineStr">
         <is>
-          <t>236220</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="29" t="inlineStr">
         <is>
-          <t>benchmark.industryType</t>
-        </is>
-      </c>
-      <c r="B435" s="13" t="inlineStr">
-        <is>
-          <t>Commercial And Institutional Building Construction</t>
-        </is>
+          <t>verifiedMonths[5].revenue</t>
+        </is>
+      </c>
+      <c r="B435" s="5" t="n">
+        <v>5199082.25</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="29" t="inlineStr">
         <is>
-          <t>benchmark.benchmarkPeriodRange</t>
-        </is>
-      </c>
-      <c r="B436" s="13" t="inlineStr">
-        <is>
-          <t>Mar 2025 - Feb 2026</t>
-        </is>
+          <t>verifiedMonths[5].cogs</t>
+        </is>
+      </c>
+      <c r="B436" s="5" t="n">
+        <v>2879916.44</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="29" t="inlineStr">
         <is>
+          <t>verifiedMonths[5].grossProfit</t>
+        </is>
+      </c>
+      <c r="B437" s="5" t="n">
+        <v>2319165.81</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[5].operatingExpenses</t>
+        </is>
+      </c>
+      <c r="B438" s="5" t="n">
+        <v>757595.17</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[5].netIncome</t>
+        </is>
+      </c>
+      <c r="B439" s="5" t="n">
+        <v>1561681.96</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[5].grossMarginPct</t>
+        </is>
+      </c>
+      <c r="B440" s="6" t="n">
+        <v>0.4460721524457514</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[5].netMarginPct</t>
+        </is>
+      </c>
+      <c r="B441" s="6" t="n">
+        <v>0.3003764674044155</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="29" t="inlineStr">
+        <is>
+          <t>verifiedMonths[5].month</t>
+        </is>
+      </c>
+      <c r="B442" s="13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.companyName</t>
+        </is>
+      </c>
+      <c r="B443" s="13" t="inlineStr">
+        <is>
+          <t>Midwest Design Group LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricType</t>
+        </is>
+      </c>
+      <c r="B444" s="13" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricLabel</t>
+        </is>
+      </c>
+      <c r="B445" s="13" t="inlineStr">
+        <is>
+          <t>Yearly Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.metricValue</t>
+        </is>
+      </c>
+      <c r="B446" s="5" t="n">
+        <v>3757685.49</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.regionalAverage</t>
+        </is>
+      </c>
+      <c r="B447" s="5" t="n">
+        <v>101486.51</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.nationalAverage</t>
+        </is>
+      </c>
+      <c r="B448" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.vsRegionalPercent</t>
+        </is>
+      </c>
+      <c r="B449" s="5" t="n">
+        <v>3602.65</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.vsNationalPercent</t>
+        </is>
+      </c>
+      <c r="B450" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.isAboveRegional</t>
+        </is>
+      </c>
+      <c r="B451" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.isAboveNational</t>
+        </is>
+      </c>
+      <c r="B452" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.location</t>
+        </is>
+      </c>
+      <c r="B453" s="13" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.naicsCode</t>
+        </is>
+      </c>
+      <c r="B454" s="13" t="inlineStr">
+        <is>
+          <t>236220</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.industryType</t>
+        </is>
+      </c>
+      <c r="B455" s="13" t="inlineStr">
+        <is>
+          <t>Commercial And Institutional Building Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="29" t="inlineStr">
+        <is>
+          <t>benchmark.benchmarkPeriodRange</t>
+        </is>
+      </c>
+      <c r="B456" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2025 - Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="29" t="inlineStr">
+        <is>
           <t>benchmark.reportDate</t>
         </is>
       </c>
-      <c r="B437" s="13" t="inlineStr">
+      <c r="B457" s="13" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
@@ -5829,7 +6041,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>YTD 2026 (2026-01-01 → 2026-05-07) vs FY 2025</t>
+          <t>YTD 2026 (2026-01-01 → 2026-07-07) vs FY 2025</t>
         </is>
       </c>
     </row>
@@ -5867,10 +6079,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30240248.32</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
       <c r="D5" s="5">
         <f>B5-C5</f>
@@ -5888,10 +6100,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>14108989.66</v>
+        <v>20292158.47</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>27755136.44</v>
+        <v>27754565.1</v>
       </c>
       <c r="D6" s="5">
         <f>B6-C6</f>
@@ -5952,10 +6164,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5403991.67</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>9925912.359999999</v>
+        <v>9926483.689999999</v>
       </c>
       <c r="D9" s="5">
         <f>B9-C9</f>
@@ -6032,7 +6244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6096,10 +6308,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30240248.32</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>39537774.9</v>
@@ -6120,10 +6332,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5267780.53</v>
+        <v>9948089.85</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>12736678.98</v>
+        <v>12737250.31</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>11102557.97</v>
@@ -6144,10 +6356,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.2718606082616702</v>
+        <v>0.3289685238272541</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.314549467537803</v>
+        <v>0.3145635773804887</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0.2808088719732179</v>
@@ -6164,10 +6376,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5403991.67</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>9925912.359999999</v>
+        <v>9926483.689999999</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>8249044.14</v>
@@ -6188,7 +6400,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4544098.18</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>2810766.62</v>
@@ -6212,10 +6424,10 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.08575153308354315</v>
+        <v>0.1502665630227206</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.06941567304022843</v>
+        <v>0.06941567305737158</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>0.07332639652415061</v>
@@ -6399,6 +6611,70 @@
       </c>
       <c r="H18" s="6">
         <f>IFERROR(G18/B18,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4925779.55</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>3335298.81</v>
+      </c>
+      <c r="D19" s="5">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="6">
+        <f>IFERROR(D19/B19,0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>978876.21</v>
+      </c>
+      <c r="G19" s="5">
+        <f>D19-F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="6">
+        <f>IFERROR(G19/B19,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>5199082.25</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>2879916.44</v>
+      </c>
+      <c r="D20" s="5">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="6">
+        <f>IFERROR(D20/B20,0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>757595.17</v>
+      </c>
+      <c r="G20" s="5">
+        <f>D20-F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="6">
+        <f>IFERROR(G20/B20,0)</f>
         <v/>
       </c>
     </row>
@@ -6469,10 +6745,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30240248.32</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
       <c r="D6" s="5">
         <f>B6-C6</f>
@@ -6486,10 +6762,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>14108989.66</v>
+        <v>20292158.47</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>27755136.44</v>
+        <v>27754565.1</v>
       </c>
       <c r="D7" s="5">
         <f>B7-C7</f>
@@ -6503,10 +6779,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>5267780.53</v>
+        <v>9948089.85</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>12736678.98</v>
+        <v>12737250.31</v>
       </c>
       <c r="D8" s="5">
         <f>B8-C8</f>
@@ -6520,10 +6796,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.2718606082616702</v>
+        <v>0.3289685238272541</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.314549467537803</v>
+        <v>0.3145635773804887</v>
       </c>
       <c r="D9" s="6">
         <f>B9-C9</f>
@@ -6537,10 +6813,10 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5403991.67</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>9925912.359999999</v>
+        <v>9926483.689999999</v>
       </c>
       <c r="D10" s="5">
         <f>B10-C10</f>
@@ -6554,7 +6830,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4544098.18</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>2810766.62</v>
@@ -6733,7 +7009,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5 of 12 months completed · 7 remaining. Year-End Forecast = YTD + (Avg Monthly × Remaining).</t>
+          <t>7 of 12 months completed · 5 remaining. Year-End Forecast = YTD + (Avg Monthly × Remaining).</t>
         </is>
       </c>
     </row>
@@ -6771,13 +7047,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30240248.32</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3875354.04</v>
+        <v>4320035.47</v>
       </c>
       <c r="D5" s="5">
-        <f>B5+C5*7</f>
+        <f>B5+C5*5</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -6792,13 +7068,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5267780.53</v>
+        <v>9948089.85</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1053556.11</v>
+        <v>1421155.69</v>
       </c>
       <c r="D6" s="5">
-        <f>B6+C6*7</f>
+        <f>B6+C6*5</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -6813,13 +7089,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>3480138.73</v>
+        <v>5403991.67</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>696027.75</v>
+        <v>771998.8100000001</v>
       </c>
       <c r="D7" s="5">
-        <f>B7+C7*7</f>
+        <f>B7+C7*5</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -6834,13 +7110,13 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4544098.18</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>332317.55</v>
+        <v>649156.88</v>
       </c>
       <c r="D8" s="5">
-        <f>B8+C8*7</f>
+        <f>B8+C8*5</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -6877,7 +7153,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-1103389.81</v>
+        <v>-857832.02</v>
       </c>
     </row>
   </sheetData>
@@ -6895,7 +7171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6983,19 +7259,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>40491815.42</v>
+        <v>40491815.41</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>12736678.98</v>
+        <v>12737250.31</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.314549467537803</v>
+        <v>0.3145635773804887</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>2810766.62</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.06941567304022843</v>
+        <v>0.06941567305737158</v>
       </c>
     </row>
     <row r="7">
@@ -7005,19 +7281,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30240248.32</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>5267780.53</v>
+        <v>9948089.85</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.2718606082616702</v>
+        <v>0.3289685238272541</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1661587.75</v>
+        <v>4544098.18</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.08575153308354315</v>
+        <v>0.1502665630227206</v>
       </c>
     </row>
     <row r="8">
@@ -7027,19 +7303,19 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>46504248.46</v>
+        <v>51840425.69</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>12642673.27</v>
+        <v>17053868.31</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.2718606081952797</v>
+        <v>0.3289685237536482</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3987810.6</v>
+        <v>7789882.59</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.08575153307616747</v>
+        <v>0.1502665629441902</v>
       </c>
     </row>
     <row r="11">
@@ -7201,6 +7477,62 @@
       </c>
       <c r="H16" s="6" t="n">
         <v>0.1474627544988424</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>4925779.55</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3335298.81</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1590480.74</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>978876.21</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>611696.3100000001</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0.3228891435062294</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.1241826402888859</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>5199082.25</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2879916.44</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2319165.81</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>757595.17</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1561681.96</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.4460721524457514</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3003764674044155</v>
       </c>
     </row>
   </sheetData>
@@ -7281,7 +7613,7 @@
         <v>20720.33</v>
       </c>
       <c r="C6" s="6">
-        <f>B6/19376770.19</f>
+        <f>B6/30240248.32</f>
         <v/>
       </c>
       <c r="D6" s="5" t="n">
@@ -7295,10 +7627,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>571765.41</v>
+        <v>997500.28</v>
       </c>
       <c r="C7" s="6">
-        <f>B7/19376770.19</f>
+        <f>B7/30240248.32</f>
         <v/>
       </c>
       <c r="D7" s="5" t="n">
@@ -7312,10 +7644,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>16823.83</v>
+        <v>16826.61</v>
       </c>
       <c r="C8" s="6">
-        <f>B8/19376770.19</f>
+        <f>B8/30240248.32</f>
         <v/>
       </c>
       <c r="D8" s="5" t="n">
@@ -7329,10 +7661,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>206725</v>
+        <v>396425</v>
       </c>
       <c r="C9" s="6">
-        <f>B9/19376770.19</f>
+        <f>B9/30240248.32</f>
         <v/>
       </c>
       <c r="D9" s="5" t="n">
@@ -7349,7 +7681,7 @@
         <v>4820</v>
       </c>
       <c r="C10" s="6">
-        <f>B10/19376770.19</f>
+        <f>B10/30240248.32</f>
         <v/>
       </c>
       <c r="D10" s="5" t="n">
@@ -7363,14 +7695,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>15924134.62</v>
+        <v>25762267.87</v>
       </c>
       <c r="C11" s="6">
-        <f>B11/19376770.19</f>
+        <f>B11/30240248.32</f>
         <v/>
       </c>
       <c r="D11" s="5" t="n">
-        <v>33721642.66</v>
+        <v>33721642.65</v>
       </c>
     </row>
     <row r="12">
@@ -7380,10 +7712,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>2347599</v>
+        <v>2544448.44</v>
       </c>
       <c r="C12" s="6">
-        <f>B12/19376770.19</f>
+        <f>B12/30240248.32</f>
         <v/>
       </c>
       <c r="D12" s="5" t="n">
@@ -7426,10 +7758,10 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>6261029.85</v>
+        <v>8828741.710000001</v>
       </c>
       <c r="C17" s="6">
-        <f>B17/14108989.66</f>
+        <f>B17/20292158.47</f>
         <v/>
       </c>
       <c r="D17" s="5" t="n">
@@ -7443,10 +7775,10 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>2745051.1</v>
+        <v>3895643.04</v>
       </c>
       <c r="C18" s="6">
-        <f>B18/14108989.66</f>
+        <f>B18/20292158.47</f>
         <v/>
       </c>
       <c r="D18" s="5" t="n">
@@ -7460,10 +7792,10 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>529849.5</v>
+        <v>799947.42</v>
       </c>
       <c r="C19" s="6">
-        <f>B19/14108989.66</f>
+        <f>B19/20292158.47</f>
         <v/>
       </c>
       <c r="D19" s="5" t="n">
@@ -7511,10 +7843,10 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1928101.09</v>
+        <v>2918142.76</v>
       </c>
       <c r="C24" s="6">
-        <f>B24/3480138.73</f>
+        <f>B24/5403991.67</f>
         <v/>
       </c>
       <c r="D24" s="5" t="n">
@@ -7532,14 +7864,14 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>757455.8100000001</v>
+        <v>1109860.58</v>
       </c>
       <c r="C25" s="6">
-        <f>B25/3480138.73</f>
+        <f>B25/5403991.67</f>
         <v/>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1286006.54</v>
+        <v>196030.17</v>
       </c>
       <c r="E25" s="6">
         <f>IFERROR((B25-D25)/ABS(D25),"")</f>
@@ -7553,10 +7885,10 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>72850.52</v>
+        <v>139754.06</v>
       </c>
       <c r="C26" s="6">
-        <f>B26/3480138.73</f>
+        <f>B26/5403991.67</f>
         <v/>
       </c>
       <c r="D26" s="5" t="n">
@@ -7574,10 +7906,10 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>191337.16</v>
+        <v>357720.02</v>
       </c>
       <c r="C27" s="6">
-        <f>B27/3480138.73</f>
+        <f>B27/5403991.67</f>
         <v/>
       </c>
       <c r="D27" s="5" t="n">
@@ -7595,10 +7927,10 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>64541.24</v>
+        <v>134589.28</v>
       </c>
       <c r="C28" s="6">
-        <f>B28/3480138.73</f>
+        <f>B28/5403991.67</f>
         <v/>
       </c>
       <c r="D28" s="5" t="n">
@@ -7616,14 +7948,14 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>221218.59</v>
+        <v>402320.28</v>
       </c>
       <c r="C29" s="6">
-        <f>B29/3480138.73</f>
+        <f>B29/5403991.67</f>
         <v/>
       </c>
       <c r="D29" s="5" t="n">
-        <v>981759.21</v>
+        <v>981248.3100000001</v>
       </c>
       <c r="E29" s="6">
         <f>IFERROR((B29-D29)/ABS(D29),"")</f>
@@ -7917,7 +8249,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>19376770.19</v>
+        <v>30240248.32</v>
       </c>
     </row>
     <row r="6">
@@ -7986,10 +8318,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>46504248.46</v>
+        <v>51840425.69</v>
       </c>
       <c r="C12" s="5">
-        <f>B5+(3875354.04*7)*(1+$B$6)</f>
+        <f>B5+(4320035.47*5)*(1+$B$6)</f>
         <v/>
       </c>
       <c r="D12" s="5">
@@ -8004,10 +8336,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0.2718606081952797</v>
+        <v>0.3289685237536482</v>
       </c>
       <c r="C13" s="6">
-        <f>0.2718606081952797+$B$7</f>
+        <f>0.3289685237536482+$B$7</f>
         <v/>
       </c>
       <c r="D13" s="6">
@@ -8022,7 +8354,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>12642673.27</v>
+        <v>17053868.31</v>
       </c>
       <c r="C14" s="5">
         <f>C12*C13</f>
@@ -8040,10 +8372,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>8352332.95</v>
+        <v>9263985.720000001</v>
       </c>
       <c r="C15" s="5">
-        <f>3480138.73+(696027.75*7)*(1+$B$8)</f>
+        <f>5403991.67+(771998.81*5)*(1+$B$8)</f>
         <v/>
       </c>
       <c r="D15" s="5">
@@ -8058,7 +8390,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>3987810.6</v>
+        <v>7789882.59</v>
       </c>
       <c r="C16" s="5">
         <f>C14-C15</f>
@@ -8076,7 +8408,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.08575153307616747</v>
+        <v>0.1502665629441902</v>
       </c>
       <c r="C17" s="6">
         <f>C16/C12</f>
